--- a/models/demo-temporal/demo-temporal.xlsx
+++ b/models/demo-temporal/demo-temporal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/projects/anse-models/demo-temporal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB94012-A3E7-0F43-83AF-2B75B7F39629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DC1ADC-BB95-7C48-A5CF-A671CBE83E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26900" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
+    <workbookView xWindow="16440" yWindow="1820" windowWidth="31340" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs - Flow Network" sheetId="1" r:id="rId1"/>
@@ -19,11 +19,8 @@
     <sheet name="Inputs - Spatial" sheetId="4" r:id="rId4"/>
     <sheet name="Inputs - Advanced Curves" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -42,365 +39,197 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Magnan, Michael</author>
-    <author>mhafer</author>
+    <author>tc={0004001B-0038-4DC0-8915-0011004800D3}</author>
+    <author>tc={005200E3-00FA-4B8B-829A-001300630028}</author>
+    <author>tc={002B00A3-0019-4FC6-8D0C-004900AF00F1}</author>
+    <author>tc={00310024-0068-4E72-996C-002400A100C5}</author>
+    <author>tc={00BF0044-0036-47FF-AABD-002D00FB0030}</author>
+    <author>tc={00750004-00F1-40F7-95F5-0062003300B3}</author>
+    <author>tc={003C00FA-00EE-470B-9255-00E300580024}</author>
+    <author>tc={001000A9-00B4-4E3A-984A-000A00DD002C}</author>
+    <author>tc={00C60005-0020-4ABD-AD97-005B002100FC}</author>
+    <author>tc={00EE00CF-001E-4137-8D9C-00BC0011005C}</author>
+    <author>tc={00480092-004A-4F25-B006-009E001100DC}</author>
+    <author>tc={002100F1-00A4-42C8-B92D-004700100045}</author>
+    <author>tc={005C003D-007F-4EA5-BD9C-004400790053}</author>
+    <author>tc={00950013-0093-4251-B266-0033000300E8}</author>
+    <author>tc={003400D0-0011-4766-8794-002B001800B6}</author>
+    <author>tc={0087004E-00F0-4527-A7D1-00DA00540077}</author>
+    <author>tc={00EC0088-00AA-48E0-BDF0-00A8009500F6}</author>
+    <author>tc={00DF0095-0069-4B0F-B060-00E0004200E3}</author>
+    <author>tc={4443FF7A-5B3E-AD43-B956-98A58508E5E4}</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{DE5AEED7-5306-0F41-A9F6-E09723C07087}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{0004001B-0038-4DC0-8915-0011004800D3}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Magnan, Michael:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    If unknown/undefined, enter "0"
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>If unknown/undefined, enter "0"</t>
-        </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{3CFD2D9D-03A4-3D43-B752-639C8A9DCDB2}">
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{005200E3-00FA-4B8B-829A-001300630028}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>mhafer:
-Not currently supported</t>
-        </r>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Not currently supported
+</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="1" shapeId="0" xr:uid="{AE144688-A2B4-F142-9E42-AB258D324434}">
+    <comment ref="H1" authorId="2" shapeId="0" xr:uid="{002B00A3-0019-4FC6-8D0C-004900AF00F1}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>mhafer:
-Not currently supported</t>
-        </r>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Not currently supported
+</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{10548B0F-45C8-2B40-81CC-02D44A03EDB8}">
+    <comment ref="I1" authorId="3" shapeId="0" xr:uid="{00310024-0068-4E72-996C-002400A100C5}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>mhafer:
-Not currently supported</t>
-        </r>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Not currently supported
+</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="1" shapeId="0" xr:uid="{79A1913B-90BC-5643-9773-44EE0531D514}">
+    <comment ref="K1" authorId="4" shapeId="0" xr:uid="{00BF0044-0036-47FF-AABD-002D00FB0030}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>mhafer:
-Not currently supported</t>
-        </r>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Not currently supported
+</t>
       </text>
     </comment>
-    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{0F0EF91A-6A2B-AF42-B0CE-76F64BCDFCAD}">
+    <comment ref="D12" authorId="5" shapeId="0" xr:uid="{00750004-00F1-40F7-95F5-0062003300B3}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Magnan, Michael:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    If unknown/undefined, enter "0"
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>If unknown/undefined, enter "0"</t>
-        </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{F5AA7D95-F276-074C-9ED4-8C923FE06A2E}">
+    <comment ref="E12" authorId="6" shapeId="0" xr:uid="{003C00FA-00EE-470B-9255-00E300580024}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Magnan, Michael:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    If unknown/undefined, enter "0"
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>If unknown/undefined, enter "0"</t>
-        </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{69409D6C-465E-1B44-BBA3-F285EDAE32E0}">
+    <comment ref="F12" authorId="7" shapeId="0" xr:uid="{001000A9-00B4-4E3A-984A-000A00DD002C}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>Magnan, Michael:
-This fiield's feature not currently supported</t>
-        </r>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This fiield's feature not currently supported
+</t>
       </text>
     </comment>
-    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{E29E9985-673B-8944-B201-8155952DC7C9}">
+    <comment ref="G12" authorId="8" shapeId="0" xr:uid="{00C60005-0020-4ABD-AD97-005B002100FC}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>Magnan, Michael:
-This fiield's feature not currently supported</t>
-        </r>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This fiield's feature not currently supported
+</t>
       </text>
     </comment>
-    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{507231BE-77FA-294B-888E-FDFACCB62F22}">
+    <comment ref="J12" authorId="9" shapeId="0" xr:uid="{00EE00CF-001E-4137-8D9C-00BC0011005C}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Magnan, Michael:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This fiield's feature not currently supported
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>This fiield's feature not currently supported</t>
-        </r>
       </text>
     </comment>
-    <comment ref="E25" authorId="1" shapeId="0" xr:uid="{9A8DBFB5-A8C4-5742-93BF-DAF4DC097001}">
+    <comment ref="E24" authorId="10" shapeId="0" xr:uid="{00480092-004A-4F25-B006-009E001100DC}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">mhafer:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Boolean field; valid values are TRUE, FALSE, 1, 0
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>Boolean field; valid values are TRUE, FALSE, 1, 0</t>
-        </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0" xr:uid="{9A461DFD-27AB-AC40-9F9F-FF5898DF7467}">
+    <comment ref="F24" authorId="11" shapeId="0" xr:uid="{002100F1-00A4-42C8-B92D-004700100045}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Magnan, Michael:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Integer field. For EVENT_POOL that is not source of carbon for the given Event, Sequence Number corresponds to an ACTION_PARAMETER_OUT component with the same sequence number
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>Integer field. For EVENT_POOL that is not source of carbon for the given Event, Sequence Number corresponds to an ACTION_PARAMETER_OUT component with the same sequence number</t>
-        </r>
       </text>
     </comment>
-    <comment ref="G25" authorId="0" shapeId="0" xr:uid="{790CC2B7-7F78-1E49-8A29-02AD544379DB}">
+    <comment ref="G24" authorId="12" shapeId="0" xr:uid="{005C003D-007F-4EA5-BD9C-004400790053}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>Magnan, Michael:
-Boolean field; valid values are TRUE, FALSE, 1, 0.
-If left empty, default is false.</t>
-        </r>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Boolean field; valid values are TRUE, FALSE, 1, 0.
+If left empty, default is false.
+</t>
       </text>
     </comment>
-    <comment ref="D41" authorId="0" shapeId="0" xr:uid="{CB8A6D56-690F-E44F-ABA7-045BB1E9BA31}">
+    <comment ref="D40" authorId="13" shapeId="0" xr:uid="{00950013-0093-4251-B266-0033000300E8}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Magnan, Michael:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    If unknown, enter name of the EVENT for which the ACTION_PARAMETER_SET will be relevant
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>If unknown, enter name of the EVENT for which the ACTION_PARAMETER_SET will be relevant</t>
-        </r>
       </text>
     </comment>
-    <comment ref="E41" authorId="0" shapeId="0" xr:uid="{0770F6B7-9594-4340-B75D-00EAD4679E04}">
+    <comment ref="E40" authorId="14" shapeId="0" xr:uid="{003400D0-0011-4766-8794-002B001800B6}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Magnan, Michael:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    If unknown, enter "UNIVERSE"
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>If unknown, enter "UNIVERSE"</t>
-        </r>
       </text>
     </comment>
-    <comment ref="F41" authorId="0" shapeId="0" xr:uid="{1B7957D1-F128-AE48-86FE-5A39ACD0DF71}">
+    <comment ref="F40" authorId="15" shapeId="0" xr:uid="{0087004E-00F0-4527-A7D1-00DA00540077}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Magnan, Michael:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Integer field
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>Integer field</t>
-        </r>
       </text>
     </comment>
-    <comment ref="G41" authorId="0" shapeId="0" xr:uid="{72DD9D24-3A22-B045-B80B-BE3842B8A588}">
+    <comment ref="G40" authorId="16" shapeId="0" xr:uid="{00EC0088-00AA-48E0-BDF0-00A8009500F6}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>Magnan, Michael:
-String field for recording notes, such as the background reference source for the parameter</t>
-        </r>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    String field for recording notes, such as the background reference source for the parameter
+</t>
       </text>
     </comment>
-    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{00E1BBAA-B86A-8842-87A5-8788FA382A41}">
+    <comment ref="D48" authorId="17" shapeId="0" xr:uid="{00DF0095-0069-4B0F-B060-00E0004200E3}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="8"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>Magnan, Michael:
-Integer field.</t>
-        </r>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Integer field.
+</t>
       </text>
     </comment>
-    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{9D0C205B-9C9C-3F4A-912F-B707A4FF980A}">
+    <comment ref="G48" authorId="18" shapeId="0" xr:uid="{4443FF7A-5B3E-AD43-B956-98A58508E5E4}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Magnan, Michael:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -410,30 +239,16 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Magnan, Michael</author>
+    <author>tc={009C0000-00FC-45D6-8AD0-00B40051008C}</author>
   </authors>
   <commentList>
-    <comment ref="B49" authorId="0" shapeId="0" xr:uid="{CC7F5D1D-B34F-1646-BA4F-A18CC3CBED25}">
+    <comment ref="B49" authorId="0" shapeId="0" xr:uid="{009C0000-00FC-45D6-8AD0-00B40051008C}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Magnan, Michael:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Not currently implemented
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>Not currently implemented</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -443,179 +258,50 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>mhafer</author>
+    <author>tc={00A00060-0088-4941-AA12-009A00A200AE}</author>
+    <author>tc={005900A6-00B4-4D8E-B8A4-00CF00700065}</author>
+    <author>tc={002800F8-00BE-4813-B18D-00EA0079002A}</author>
+    <author>tc={008C0089-0086-46C3-8B79-00E100B6003A}</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{EA202CC9-29F3-D843-B152-881A2002777E}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00A00060-0088-4941-AA12-009A00A200AE}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">mhafer:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Integer field - must be entered here as …
+=TEXT(value, "0")
+where value can be any valid Excel expression that resolves to an integer value
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Integer field - must be entered here as …
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">=TEXT(value, "0")
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>where value can be any valid Excel expression that resolves to an integer value</t>
-        </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{1C18341E-17CA-F744-B49C-E9ECBCC81AB6}">
+    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{005900A6-00B4-4D8E-B8A4-00CF00700065}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">mhafer:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Technically this field is not required, but it is good practice to provide a value 
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Technically this field is not required, but it is good practice to provide a value </t>
-        </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{F0CC4848-5E49-0041-B3D5-0A6D38AC9A79}">
+    <comment ref="E1" authorId="2" shapeId="0" xr:uid="{002800F8-00BE-4813-B18D-00EA0079002A}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">mhafer:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Technically this field is not required, but it is good practice to provide a value 
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Technically this field is not required, but it is good practice to provide a value </t>
-        </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{0D59C2D4-07A0-9147-B057-CE565E9CA9C6}">
+    <comment ref="G1" authorId="3" shapeId="0" xr:uid="{008C0089-0086-46C3-8B79-00E100B6003A}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">mhafer:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Integer field - must be entered here as …
+=TEXT(value, "0")
+where value can be any valid Excel expression that resolves to an integer value
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Integer field - must be entered here as …
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">=TEXT(value, "0")
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>where value can be any valid Excel expression that resolves to an integer value</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -683,6 +369,15 @@
     <t>POOL</t>
   </si>
   <si>
+    <t>IPCC default-sawnwood</t>
+  </si>
+  <si>
+    <t>IPCC default-panels</t>
+  </si>
+  <si>
+    <t>IPCC default-paper</t>
+  </si>
+  <si>
     <t>Keyword: EVENT</t>
   </si>
   <si>
@@ -716,6 +411,18 @@
     <t>NAME</t>
   </si>
   <si>
+    <t>ACTION_TYPE</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Landfilling</t>
+  </si>
+  <si>
+    <t>Combusting</t>
+  </si>
+  <si>
     <t>Keyword: EVENT_POOL</t>
   </si>
   <si>
@@ -755,177 +462,267 @@
     <t>ACTION_PARAMETER_SET</t>
   </si>
   <si>
+    <t>Keyword: ACTION_PARAMETER_OUT</t>
+  </si>
+  <si>
+    <t>Action_Parameter_Set(Name)</t>
+  </si>
+  <si>
+    <t>Proportion</t>
+  </si>
+  <si>
+    <t>New Physical State Name</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>ACTION_PARAMETER_OUT</t>
+  </si>
+  <si>
+    <t>Keyword: INITIAL_CMO</t>
+  </si>
+  <si>
+    <t>Entry Pool (Pool Name)</t>
+  </si>
+  <si>
+    <t>Species (Name)</t>
+  </si>
+  <si>
+    <t>Physical State (Name)</t>
+  </si>
+  <si>
+    <t>Quantity (Double precison)</t>
+  </si>
+  <si>
+    <t>Entry Time Step (Integer)</t>
+  </si>
+  <si>
+    <t>Initial Age</t>
+  </si>
+  <si>
+    <t>Tag (Name)</t>
+  </si>
+  <si>
+    <t>Is Retained</t>
+  </si>
+  <si>
+    <t>INITIAL_CMO</t>
+  </si>
+  <si>
+    <t>Keyword: PHYSICAL_STATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description </t>
+  </si>
+  <si>
+    <t>PHYSICAL_STATE</t>
+  </si>
+  <si>
+    <t>Roundwood</t>
+  </si>
+  <si>
+    <t>&gt; 8"</t>
+  </si>
+  <si>
+    <t>6-8"</t>
+  </si>
+  <si>
+    <t>&lt; 6" clean</t>
+  </si>
+  <si>
+    <t>&lt; 2" or contaminated</t>
+  </si>
+  <si>
+    <t>Sawnwood</t>
+  </si>
+  <si>
+    <t>Panels</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Bioenergy</t>
+  </si>
+  <si>
+    <t>Keyword: PHYSICAL_STATE_GROUP</t>
+  </si>
+  <si>
+    <t>Keyword: PHYSICAL_STATE_GROUP_MEMBER</t>
+  </si>
+  <si>
+    <t>Group(Name)</t>
+  </si>
+  <si>
+    <t>Physical_State(Name)</t>
+  </si>
+  <si>
+    <t>Keyword: SPECIES</t>
+  </si>
+  <si>
+    <t>Alternate_Name</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>SPECIES</t>
+  </si>
+  <si>
+    <t>Spruce</t>
+  </si>
+  <si>
+    <t>Pine</t>
+  </si>
+  <si>
+    <t>Fir</t>
+  </si>
+  <si>
+    <t>Hemlock</t>
+  </si>
+  <si>
+    <t>Douglas-fir</t>
+  </si>
+  <si>
+    <t>Larch</t>
+  </si>
+  <si>
+    <t>Aspen</t>
+  </si>
+  <si>
+    <t>Keyword: SPECIES_GROUP</t>
+  </si>
+  <si>
+    <t>SPECIES_GROUP</t>
+  </si>
+  <si>
+    <t>SPF</t>
+  </si>
+  <si>
+    <t>Hardwood</t>
+  </si>
+  <si>
+    <t>Hem-Fir</t>
+  </si>
+  <si>
+    <t>DFL</t>
+  </si>
+  <si>
+    <t>Keyword: SPECIES_GROUP_MEMBER</t>
+  </si>
+  <si>
+    <t>Species_Group(Name)</t>
+  </si>
+  <si>
+    <t>Species(Name)</t>
+  </si>
+  <si>
+    <t>SPECIES_GROUP_MEMBER</t>
+  </si>
+  <si>
+    <t>Keyword: TAG</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Keyword: ASU</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Tag(Name)</t>
+  </si>
+  <si>
+    <t>GIS_Id</t>
+  </si>
+  <si>
+    <t>ASU</t>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>Keyword: ASU_GROUP_TYPE</t>
+  </si>
+  <si>
+    <t>ASU_GROUP_TYPE</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Keyword: ASU_GROUP</t>
+  </si>
+  <si>
+    <t>ASU_Group_Type(Name)</t>
+  </si>
+  <si>
+    <t>ASU_GROUP</t>
+  </si>
+  <si>
+    <t>Keyword: ASU_GROUP_MEMBER</t>
+  </si>
+  <si>
+    <t>ASU(ID)</t>
+  </si>
+  <si>
+    <t>Includes: ASU_Group(Name)</t>
+  </si>
+  <si>
+    <t>ASU_GROUP_MEMBER</t>
+  </si>
+  <si>
+    <t>Keyword: CURVE</t>
+  </si>
+  <si>
+    <t>Usage</t>
+  </si>
+  <si>
+    <t>CURVE</t>
+  </si>
+  <si>
+    <t>Gamma (2.07 80.2)</t>
+  </si>
+  <si>
+    <t>initial</t>
+  </si>
+  <si>
+    <t>Xie, 2015</t>
+  </si>
+  <si>
+    <t>Keyword: CURVE_TYPE</t>
+  </si>
+  <si>
+    <t>CURVE_TYPE</t>
+  </si>
+  <si>
+    <t>US Residential Gamma Retention</t>
+  </si>
+  <si>
+    <t>Keyword: CURVE_TYPE_MEMBER</t>
+  </si>
+  <si>
+    <t>Curve_Type(Name)</t>
+  </si>
+  <si>
+    <t>Curve(Name)</t>
+  </si>
+  <si>
+    <t>Effective start timestep</t>
+  </si>
+  <si>
+    <t>CURVE_TYPE_MEMBER</t>
+  </si>
+  <si>
     <t>UNIVERSE</t>
   </si>
   <si>
-    <t>Keyword: ACTION_PARAMETER_OUT</t>
-  </si>
-  <si>
-    <t>Action_Parameter_Set(Name)</t>
-  </si>
-  <si>
-    <t>Proportion</t>
-  </si>
-  <si>
-    <t>Target Amount (Double precison)</t>
-  </si>
-  <si>
-    <t>New Physical State Name</t>
-  </si>
-  <si>
-    <t>Filter By Physical State Name/Group</t>
-  </si>
-  <si>
-    <t>Filter By Species Name/Group</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>ACTION_PARAMETER_OUT</t>
-  </si>
-  <si>
-    <t>Keyword: INITIAL_CMO</t>
-  </si>
-  <si>
-    <t>Entry Pool (Pool Name)</t>
-  </si>
-  <si>
-    <t>Species (Name)</t>
-  </si>
-  <si>
-    <t>Physical State (Name)</t>
-  </si>
-  <si>
-    <t>Quantity (Double precison)</t>
-  </si>
-  <si>
-    <t>Entry Time Step (Integer)</t>
-  </si>
-  <si>
-    <t>INITIAL_CMO</t>
-  </si>
-  <si>
-    <t>IPCC default-paper</t>
-  </si>
-  <si>
-    <t>IPCC default-sawnwood</t>
-  </si>
-  <si>
-    <t>IPCC default-panels</t>
-  </si>
-  <si>
-    <t>Keyword: PHYSICAL_STATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description </t>
-  </si>
-  <si>
-    <t>PHYSICAL_STATE</t>
-  </si>
-  <si>
-    <t>Keyword: PHYSICAL_STATE_GROUP</t>
-  </si>
-  <si>
-    <t>Keyword: PHYSICAL_STATE_GROUP_MEMBER</t>
-  </si>
-  <si>
-    <t>Group(Name)</t>
-  </si>
-  <si>
-    <t>Physical_State(Name)</t>
-  </si>
-  <si>
-    <t>Keyword: SPECIES</t>
-  </si>
-  <si>
-    <t>Alternate_Name</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Keyword: SPECIES_GROUP</t>
-  </si>
-  <si>
-    <t>Keyword: SPECIES_GROUP_MEMBER</t>
-  </si>
-  <si>
-    <t>Species_Group(Name)</t>
-  </si>
-  <si>
-    <t>Species(Name)</t>
-  </si>
-  <si>
-    <t>Keyword: TAG</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Keyword: ASU</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Area</t>
-  </si>
-  <si>
-    <t>ASU</t>
-  </si>
-  <si>
-    <t>Keyword: ASU_GROUP_TYPE</t>
-  </si>
-  <si>
-    <t>ASU_GROUP_TYPE</t>
-  </si>
-  <si>
-    <t>Keyword: ASU_GROUP</t>
-  </si>
-  <si>
-    <t>ASU_Group_Type(Name)</t>
-  </si>
-  <si>
-    <t>ASU_GROUP</t>
-  </si>
-  <si>
-    <t>Keyword: ASU_GROUP_MEMBER</t>
-  </si>
-  <si>
-    <t>ASU(ID)</t>
-  </si>
-  <si>
-    <t>ASU_GROUP_MEMBER</t>
-  </si>
-  <si>
-    <t>Tag(Name)</t>
-  </si>
-  <si>
-    <t>GIS_Id</t>
-  </si>
-  <si>
-    <t>Includes: ASU_Group(Name)</t>
-  </si>
-  <si>
-    <t>Keyword: CURVE</t>
-  </si>
-  <si>
-    <t>Keyword: CURVE_TYPE</t>
-  </si>
-  <si>
-    <t>Keyword: CURVE_TYPE_MEMBER</t>
-  </si>
-  <si>
-    <t>Curve_Type(Name)</t>
-  </si>
-  <si>
-    <t>Curve(Name)</t>
-  </si>
-  <si>
-    <t>Effective start timestep</t>
-  </si>
-  <si>
     <t>Keyword: CURVE_POINT</t>
   </si>
   <si>
@@ -935,151 +732,27 @@
     <t>Y_axis (Dependent Variable)</t>
   </si>
   <si>
-    <t>Usage</t>
-  </si>
-  <si>
-    <t>Is Retained</t>
-  </si>
-  <si>
-    <t>Initial Age</t>
-  </si>
-  <si>
-    <t>Tag (Name)</t>
-  </si>
-  <si>
-    <t>CURVE</t>
-  </si>
-  <si>
-    <t>initial</t>
-  </si>
-  <si>
-    <t>Gamma (2.07 80.2)</t>
-  </si>
-  <si>
     <t>CURVE_POINT</t>
   </si>
   <si>
-    <t>US Residential Gamma Retention</t>
-  </si>
-  <si>
-    <t>CURVE_TYPE_MEMBER</t>
-  </si>
-  <si>
-    <t>CURVE_TYPE</t>
-  </si>
-  <si>
-    <t>Xie, 2015</t>
-  </si>
-  <si>
-    <t>Roundwood</t>
-  </si>
-  <si>
-    <t>SPECIES</t>
-  </si>
-  <si>
-    <t>ACTION_TYPE</t>
-  </si>
-  <si>
-    <t>Manufacturing</t>
-  </si>
-  <si>
-    <t>Landfilling</t>
-  </si>
-  <si>
-    <t>Combusting</t>
-  </si>
-  <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <t>CAT</t>
-  </si>
-  <si>
-    <t>SPF</t>
-  </si>
-  <si>
-    <t>Aspen</t>
-  </si>
-  <si>
-    <t>DFL</t>
-  </si>
-  <si>
-    <t>Hem-Fir</t>
-  </si>
-  <si>
-    <t>SPECIES_GROUP</t>
-  </si>
-  <si>
-    <t>Spruce</t>
-  </si>
-  <si>
-    <t>Pine</t>
-  </si>
-  <si>
-    <t>Fir</t>
-  </si>
-  <si>
-    <t>Hemlock</t>
-  </si>
-  <si>
-    <t>Douglas-fir</t>
-  </si>
-  <si>
-    <t>Larch</t>
-  </si>
-  <si>
-    <t>SPECIES_GROUP_MEMBER</t>
-  </si>
-  <si>
-    <t>Hardwood</t>
-  </si>
-  <si>
-    <t>&gt; 8"</t>
-  </si>
-  <si>
-    <t>6-8"</t>
-  </si>
-  <si>
-    <t>&lt; 6" clean</t>
-  </si>
-  <si>
-    <t>&lt; 2" or contaminated</t>
-  </si>
-  <si>
-    <t>Sawnwood</t>
-  </si>
-  <si>
-    <t>Panels</t>
-  </si>
-  <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Bioenergy</t>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Physical State Rule</t>
+  </si>
+  <si>
+    <t>Species Rule</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="HelveticaNeue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1089,13 +762,12 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="HelveticaNeue"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="HelveticaNeue"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1109,7 +781,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -1125,34 +797,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF99"/>
+          <fgColor indexed="43"/>
+          <bgColor indexed="43"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF99"/>
+          <fgColor indexed="43"/>
+          <bgColor indexed="43"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1167,6 +834,14 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="mhafer" id="{A78E9034-DBB9-2373-FAC0-34FCCC144AFF}" userId="" providerId=""/>
+  <person displayName="Magnan, Michael" id="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" userId="" providerId=""/>
+  <person displayName="Magnan, Michael" id="{9DBDE2E9-6D45-4EED-C2B5-74133F8B474F}" userId="" providerId=""/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1212,108 +887,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Aptos Display"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Aptos Narrow"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1321,7 +902,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1347,7 +928,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1424,7 +1005,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1456,7 +1037,7 @@
   </a:themeElements>
   <a:objectDefaults>
     <a:lnDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -1476,17 +1057,128 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D1" personId="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" id="{0004001B-0038-4DC0-8915-0011004800D3}">
+    <text xml:space="preserve">If unknown/undefined, enter "0"
+</text>
+  </threadedComment>
+  <threadedComment ref="F1" personId="{A78E9034-DBB9-2373-FAC0-34FCCC144AFF}" id="{005200E3-00FA-4B8B-829A-001300630028}">
+    <text xml:space="preserve">Not currently supported
+</text>
+  </threadedComment>
+  <threadedComment ref="H1" personId="{A78E9034-DBB9-2373-FAC0-34FCCC144AFF}" id="{002B00A3-0019-4FC6-8D0C-004900AF00F1}">
+    <text xml:space="preserve">Not currently supported
+</text>
+  </threadedComment>
+  <threadedComment ref="I1" personId="{A78E9034-DBB9-2373-FAC0-34FCCC144AFF}" id="{00310024-0068-4E72-996C-002400A100C5}">
+    <text xml:space="preserve">Not currently supported
+</text>
+  </threadedComment>
+  <threadedComment ref="K1" personId="{A78E9034-DBB9-2373-FAC0-34FCCC144AFF}" id="{00BF0044-0036-47FF-AABD-002D00FB0030}">
+    <text xml:space="preserve">Not currently supported
+</text>
+  </threadedComment>
+  <threadedComment ref="D12" personId="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" id="{00750004-00F1-40F7-95F5-0062003300B3}">
+    <text xml:space="preserve">If unknown/undefined, enter "0"
+</text>
+  </threadedComment>
+  <threadedComment ref="E12" personId="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" id="{003C00FA-00EE-470B-9255-00E300580024}">
+    <text xml:space="preserve">If unknown/undefined, enter "0"
+</text>
+  </threadedComment>
+  <threadedComment ref="F12" personId="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" id="{001000A9-00B4-4E3A-984A-000A00DD002C}">
+    <text xml:space="preserve">This fiield's feature not currently supported
+</text>
+  </threadedComment>
+  <threadedComment ref="G12" personId="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" id="{00C60005-0020-4ABD-AD97-005B002100FC}">
+    <text xml:space="preserve">This fiield's feature not currently supported
+</text>
+  </threadedComment>
+  <threadedComment ref="J12" personId="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" id="{00EE00CF-001E-4137-8D9C-00BC0011005C}">
+    <text xml:space="preserve">This fiield's feature not currently supported
+</text>
+  </threadedComment>
+  <threadedComment ref="E24" personId="{A78E9034-DBB9-2373-FAC0-34FCCC144AFF}" id="{00480092-004A-4F25-B006-009E001100DC}">
+    <text xml:space="preserve">Boolean field; valid values are TRUE, FALSE, 1, 0
+</text>
+  </threadedComment>
+  <threadedComment ref="F24" personId="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" id="{002100F1-00A4-42C8-B92D-004700100045}">
+    <text xml:space="preserve">Integer field. For EVENT_POOL that is not source of carbon for the given Event, Sequence Number corresponds to an ACTION_PARAMETER_OUT component with the same sequence number
+</text>
+  </threadedComment>
+  <threadedComment ref="G24" personId="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" id="{005C003D-007F-4EA5-BD9C-004400790053}">
+    <text xml:space="preserve">Boolean field; valid values are TRUE, FALSE, 1, 0.
+If left empty, default is false.
+</text>
+  </threadedComment>
+  <threadedComment ref="D40" personId="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" id="{00950013-0093-4251-B266-0033000300E8}">
+    <text xml:space="preserve">If unknown, enter name of the EVENT for which the ACTION_PARAMETER_SET will be relevant
+</text>
+  </threadedComment>
+  <threadedComment ref="E40" personId="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" id="{003400D0-0011-4766-8794-002B001800B6}">
+    <text xml:space="preserve">If unknown, enter "UNIVERSE"
+</text>
+  </threadedComment>
+  <threadedComment ref="F40" personId="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" id="{0087004E-00F0-4527-A7D1-00DA00540077}">
+    <text xml:space="preserve">Integer field
+</text>
+  </threadedComment>
+  <threadedComment ref="G40" personId="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" id="{00EC0088-00AA-48E0-BDF0-00A8009500F6}">
+    <text xml:space="preserve">String field for recording notes, such as the background reference source for the parameter
+</text>
+  </threadedComment>
+  <threadedComment ref="D48" personId="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" id="{00DF0095-0069-4B0F-B060-00E0004200E3}">
+    <text xml:space="preserve">Integer field.
+</text>
+  </threadedComment>
+  <threadedComment ref="G48" personId="{4BD0F246-EAAB-D612-C49A-BCF5CC83D356}" id="{4443FF7A-5B3E-AD43-B956-98A58508E5E4}">
+    <text xml:space="preserve">The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B49" personId="{9DBDE2E9-6D45-4EED-C2B5-74133F8B474F}" id="{009C0000-00FC-45D6-8AD0-00B40051008C}">
+    <text xml:space="preserve">Not currently implemented
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C1" personId="{A78E9034-DBB9-2373-FAC0-34FCCC144AFF}" id="{00A00060-0088-4941-AA12-009A00A200AE}">
+    <text xml:space="preserve">Integer field - must be entered here as …
+=TEXT(value, "0")
+where value can be any valid Excel expression that resolves to an integer value
+</text>
+  </threadedComment>
+  <threadedComment ref="D1" personId="{A78E9034-DBB9-2373-FAC0-34FCCC144AFF}" id="{005900A6-00B4-4D8E-B8A4-00CF00700065}">
+    <text xml:space="preserve">Technically this field is not required, but it is good practice to provide a value 
+</text>
+  </threadedComment>
+  <threadedComment ref="E1" personId="{A78E9034-DBB9-2373-FAC0-34FCCC144AFF}" id="{002800F8-00BE-4813-B18D-00EA0079002A}">
+    <text xml:space="preserve">Technically this field is not required, but it is good practice to provide a value 
+</text>
+  </threadedComment>
+  <threadedComment ref="G1" personId="{A78E9034-DBB9-2373-FAC0-34FCCC144AFF}" id="{008C0089-0086-46C3-8B79-00E100B6003A}">
+    <text xml:space="preserve">Integer field - must be entered here as …
+=TEXT(value, "0")
+where value can be any valid Excel expression that resolves to an integer value
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F935C300-5F44-C54A-ADD4-2A504DCCAD49}">
-  <dimension ref="B1:L113"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:L112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5703125" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -1564,7 +1256,7 @@
         <v>1725</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="16" customHeight="1">
@@ -1580,7 +1272,7 @@
         <v>1725</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="16" customHeight="1">
@@ -1596,14 +1288,14 @@
         <v>1725</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="16" customHeight="1">
       <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4" t="str">
+      <c r="C8" s="3" t="str">
         <f>"Bioenergy, "&amp;'Inputs - Spatial'!$C$10</f>
         <v>Bioenergy, CAT</v>
       </c>
@@ -1625,51 +1317,51 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="12" spans="2:12" s="3" customFormat="1" ht="16" customHeight="1">
+    <row r="12" spans="2:12" s="1" customFormat="1" ht="16" customHeight="1">
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="F12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="G12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="H12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="I12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="16" customHeight="1">
       <c r="B14" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C14" t="str">
         <f>"Manufacturing, "&amp;'Inputs - Spatial'!C10</f>
         <v>Manufacturing, CAT</v>
       </c>
       <c r="D14" t="str">
-        <f>C20</f>
+        <f t="shared" ref="D14:D16" si="0">C20</f>
         <v>Manufacturing</v>
       </c>
       <c r="E14">
@@ -1679,14 +1371,14 @@
     </row>
     <row r="15" spans="2:12" ht="16" customHeight="1">
       <c r="B15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C15" t="str">
         <f>"Landfilling, "&amp;'Inputs - Spatial'!$C$10</f>
         <v>Landfilling, CAT</v>
       </c>
       <c r="D15" t="str">
-        <f>C21</f>
+        <f t="shared" si="0"/>
         <v>Landfilling</v>
       </c>
       <c r="E15">
@@ -1696,14 +1388,14 @@
     </row>
     <row r="16" spans="2:12" ht="16" customHeight="1">
       <c r="B16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C16" t="str">
         <f>"Combusting, "&amp;'Inputs - Spatial'!$C$10</f>
         <v>Combusting, CAT</v>
       </c>
       <c r="D16" t="str">
-        <f>C22</f>
+        <f t="shared" si="0"/>
         <v>Combusting</v>
       </c>
       <c r="E16">
@@ -1711,72 +1403,91 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="18" spans="2:7" s="3" customFormat="1" ht="16" customHeight="1">
+    <row r="18" spans="2:7" s="1" customFormat="1" ht="16" customHeight="1">
       <c r="B18" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="16" customHeight="1">
       <c r="B20" t="s">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="16" customHeight="1">
       <c r="B21" t="s">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="16" customHeight="1">
       <c r="B22" t="s">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" s="3" customFormat="1" ht="16" customHeight="1">
-      <c r="B25" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" s="1" customFormat="1" ht="16" customHeight="1">
+      <c r="B24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="16" customHeight="1">
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" ref="C26:C30" si="1">$C$14</f>
+        <v>Manufacturing, CAT</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" ref="D26:D29" si="2">C3</f>
+        <v>Roundwood, CAT</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="16" customHeight="1">
       <c r="B27" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C27" t="str">
-        <f>$C$14</f>
+        <f t="shared" si="1"/>
         <v>Manufacturing, CAT</v>
       </c>
       <c r="D27" t="str">
-        <f>C3</f>
-        <v>Roundwood, CAT</v>
+        <f t="shared" si="2"/>
+        <v>Sawnwood, CAT</v>
       </c>
       <c r="E27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -1784,227 +1495,228 @@
     </row>
     <row r="28" spans="2:7" ht="16" customHeight="1">
       <c r="B28" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C28" t="str">
-        <f t="shared" ref="C28:C31" si="0">$C$14</f>
+        <f t="shared" si="1"/>
         <v>Manufacturing, CAT</v>
       </c>
       <c r="D28" t="str">
-        <f>C4</f>
-        <v>Sawnwood, CAT</v>
+        <f t="shared" si="2"/>
+        <v>Panels, CAT</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="16" customHeight="1">
       <c r="B29" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C29" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Manufacturing, CAT</v>
       </c>
       <c r="D29" t="str">
-        <f>C5</f>
-        <v>Panels, CAT</v>
+        <f t="shared" si="2"/>
+        <v>Paper, CAT</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="16" customHeight="1">
       <c r="B30" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C30" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Manufacturing, CAT</v>
       </c>
       <c r="D30" t="str">
-        <f>C6</f>
-        <v>Paper, CAT</v>
+        <f>C8</f>
+        <v>Bioenergy, CAT</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="16" customHeight="1">
-      <c r="B31" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" t="str">
-        <f t="shared" si="0"/>
-        <v>Manufacturing, CAT</v>
-      </c>
-      <c r="D31" t="str">
-        <f>C8</f>
-        <v>Bioenergy, CAT</v>
-      </c>
-      <c r="E31" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="16" customHeight="1">
+    <row r="32" spans="2:7" ht="16" customHeight="1">
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" t="str" cm="1">
+        <f t="array" ref="C32">$C$15</f>
+        <v>Landfilling, CAT</v>
+      </c>
+      <c r="D32" t="str">
+        <f t="shared" ref="D32:D34" si="3">C4</f>
+        <v>Sawnwood, CAT</v>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" ht="16" customHeight="1">
       <c r="B33" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C33" t="str" cm="1">
         <f t="array" ref="C33">$C$15</f>
         <v>Landfilling, CAT</v>
       </c>
       <c r="D33" t="str">
-        <f>C4</f>
-        <v>Sawnwood, CAT</v>
+        <f t="shared" si="3"/>
+        <v>Panels, CAT</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" ht="16" customHeight="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" ht="16" customHeight="1">
       <c r="B34" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C34" t="str" cm="1">
         <f t="array" ref="C34">$C$15</f>
         <v>Landfilling, CAT</v>
       </c>
       <c r="D34" t="str">
-        <f>C5</f>
-        <v>Panels, CAT</v>
+        <f t="shared" si="3"/>
+        <v>Paper, CAT</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
       <c r="F34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" ht="16" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" ht="16" customHeight="1">
       <c r="B35" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C35" t="str" cm="1">
         <f t="array" ref="C35">$C$15</f>
         <v>Landfilling, CAT</v>
       </c>
       <c r="D35" t="str">
-        <f>C6</f>
-        <v>Paper, CAT</v>
-      </c>
-      <c r="E35" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" ht="16" customHeight="1">
-      <c r="B36" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" t="str" cm="1">
-        <f t="array" ref="C36">$C$15</f>
-        <v>Landfilling, CAT</v>
-      </c>
-      <c r="D36" t="str">
         <f>C10</f>
         <v>CO2, CAT</v>
       </c>
-      <c r="E36" t="b">
+      <c r="E35" t="b">
         <v>0</v>
       </c>
-      <c r="F36">
+      <c r="F35">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="16" customHeight="1">
-      <c r="B38" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" t="str">
-        <f>$C$16</f>
+    <row r="37" spans="2:10" ht="16" customHeight="1">
+      <c r="B37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" t="str">
+        <f t="shared" ref="C37:C38" si="4">$C$16</f>
         <v>Combusting, CAT</v>
       </c>
-      <c r="D38" t="str">
+      <c r="D37" t="str">
         <f>C8</f>
         <v>Bioenergy, CAT</v>
       </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" ht="16" customHeight="1">
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="4"/>
+        <v>Combusting, CAT</v>
+      </c>
+      <c r="D38" t="str">
+        <f>C10</f>
+        <v>CO2, CAT</v>
+      </c>
       <c r="E38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="16" customHeight="1">
-      <c r="B39" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" t="str">
-        <f>$C$16</f>
-        <v>Combusting, CAT</v>
-      </c>
-      <c r="D39" t="str">
-        <f>C10</f>
-        <v>CO2, CAT</v>
-      </c>
-      <c r="E39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39">
+    <row r="40" spans="2:10" s="1" customFormat="1" ht="16" customHeight="1">
+      <c r="B40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="2:8" s="3" customFormat="1" ht="16" customHeight="1">
-      <c r="B41" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="D40" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" ht="16" customHeight="1">
+      <c r="B42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" t="str">
+        <f>"Commodity Demand, "&amp;F42&amp;", "&amp;'Inputs - Spatial'!$C$10</f>
+        <v>Commodity Demand, 1, CAT</v>
+      </c>
+      <c r="D42" t="str">
+        <f t="shared" ref="D42:D44" si="5">$C$20</f>
+        <v>Manufacturing</v>
+      </c>
+      <c r="E42" t="str">
+        <f>'Inputs - Spatial'!$C$10</f>
+        <v>CAT</v>
+      </c>
+      <c r="F42">
         <v>1</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" ht="16" customHeight="1">
+    </row>
+    <row r="43" spans="2:10" ht="16" customHeight="1">
       <c r="B43" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C43" t="str">
         <f>"Commodity Demand, "&amp;F43&amp;", "&amp;'Inputs - Spatial'!$C$10</f>
-        <v>Commodity Demand, 1, CAT</v>
+        <v>Commodity Demand, 2, CAT</v>
       </c>
       <c r="D43" t="str">
-        <f>$C$20</f>
+        <f t="shared" si="5"/>
         <v>Manufacturing</v>
       </c>
       <c r="E43" t="str">
@@ -2012,19 +1724,19 @@
         <v>CAT</v>
       </c>
       <c r="F43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" ht="16" customHeight="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" ht="16" customHeight="1">
       <c r="B44" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C44" t="str">
         <f>"Commodity Demand, "&amp;F44&amp;", "&amp;'Inputs - Spatial'!$C$10</f>
-        <v>Commodity Demand, 2, CAT</v>
+        <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D44" t="str">
-        <f t="shared" ref="D44:D45" si="1">$C$20</f>
+        <f t="shared" si="5"/>
         <v>Manufacturing</v>
       </c>
       <c r="E44" t="str">
@@ -2032,40 +1744,40 @@
         <v>CAT</v>
       </c>
       <c r="F44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" ht="16" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" ht="16" customHeight="1">
       <c r="B45" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C45" t="str">
-        <f>"Commodity Demand, "&amp;F45&amp;", "&amp;'Inputs - Spatial'!$C$10</f>
-        <v>Commodity Demand, 3, CAT</v>
+        <f>"Landfill Parameters, "&amp;'Inputs - Spatial'!$C$10</f>
+        <v>Landfill Parameters, CAT</v>
       </c>
       <c r="D45" t="str">
-        <f t="shared" si="1"/>
-        <v>Manufacturing</v>
+        <f t="shared" ref="D45:D46" si="6">C21</f>
+        <v>Landfilling</v>
       </c>
       <c r="E45" t="str">
         <f>'Inputs - Spatial'!$C$10</f>
         <v>CAT</v>
       </c>
       <c r="F45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" ht="16" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="16" customHeight="1">
       <c r="B46" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C46" t="str">
-        <f>"Landfill Parameters, "&amp;'Inputs - Spatial'!$C$10</f>
-        <v>Landfill Parameters, CAT</v>
+        <f>"Combustion Parameters, "&amp;'Inputs - Spatial'!$C$10</f>
+        <v>Combustion Parameters, CAT</v>
       </c>
       <c r="D46" t="str">
-        <f>C21</f>
-        <v>Landfilling</v>
+        <f t="shared" si="6"/>
+        <v>Combusting</v>
       </c>
       <c r="E46" t="str">
         <f>'Inputs - Spatial'!$C$10</f>
@@ -2075,361 +1787,365 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="16" customHeight="1">
-      <c r="B47" t="s">
-        <v>35</v>
-      </c>
-      <c r="C47" t="str">
-        <f>"Combustion Parameters, "&amp;'Inputs - Spatial'!$C$10</f>
-        <v>Combustion Parameters, CAT</v>
-      </c>
-      <c r="D47" t="str">
-        <f>C22</f>
-        <v>Combusting</v>
-      </c>
-      <c r="E47" t="str">
-        <f>'Inputs - Spatial'!$C$10</f>
-        <v>CAT</v>
-      </c>
-      <c r="F47">
+    <row r="48" spans="2:10" s="1" customFormat="1" ht="16" customHeight="1">
+      <c r="B48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" ht="16" customHeight="1">
+      <c r="B50" t="s">
+        <v>48</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" ref="C50:C73" si="7">$C$42</f>
+        <v>Commodity Demand, 1, CAT</v>
+      </c>
+      <c r="D50">
+        <f>$F$27</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="2:10" s="3" customFormat="1" ht="16" customHeight="1">
-      <c r="B49" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" ht="16" customHeight="1">
+      <c r="E50">
+        <v>0.4</v>
+      </c>
+      <c r="G50" t="str">
+        <f>'Inputs - Categorical'!C10</f>
+        <v>Sawnwood</v>
+      </c>
+      <c r="I50" t="str">
+        <f>'Inputs - Categorical'!$C$31</f>
+        <v>SPF</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" ht="16" customHeight="1">
       <c r="B51" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C51" t="str">
-        <f>$C$43</f>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D51">
         <f>$F$28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G51" t="str">
-        <f>'Inputs - Categorical'!C10</f>
-        <v>Sawnwood</v>
+        <f>'Inputs - Categorical'!C11</f>
+        <v>Panels</v>
       </c>
       <c r="I51" t="str">
         <f>'Inputs - Categorical'!$C$31</f>
         <v>SPF</v>
       </c>
     </row>
-    <row r="52" spans="2:10" ht="16" customHeight="1">
+    <row r="52" spans="2:9" ht="16" customHeight="1">
       <c r="B52" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C52" t="str">
-        <f t="shared" ref="C52:C54" si="2">$C$43</f>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D52">
         <f>$F$29</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G52" t="str">
-        <f>'Inputs - Categorical'!C11</f>
-        <v>Panels</v>
+        <f>'Inputs - Categorical'!C12</f>
+        <v>Paper</v>
       </c>
       <c r="I52" t="str">
         <f>'Inputs - Categorical'!$C$31</f>
         <v>SPF</v>
       </c>
     </row>
-    <row r="53" spans="2:10" ht="16" customHeight="1">
+    <row r="53" spans="2:9" ht="16" customHeight="1">
       <c r="B53" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C53" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D53">
         <f>$F$30</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="G53" t="str">
-        <f>'Inputs - Categorical'!C12</f>
-        <v>Paper</v>
+        <f>'Inputs - Categorical'!C13</f>
+        <v>Bioenergy</v>
       </c>
       <c r="I53" t="str">
         <f>'Inputs - Categorical'!$C$31</f>
         <v>SPF</v>
       </c>
     </row>
-    <row r="54" spans="2:10" ht="16" customHeight="1">
-      <c r="B54" t="s">
-        <v>45</v>
-      </c>
-      <c r="C54" t="str">
-        <f t="shared" si="2"/>
+    <row r="55" spans="2:9" ht="16" customHeight="1">
+      <c r="B55" t="s">
+        <v>48</v>
+      </c>
+      <c r="C55" t="str">
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
-      <c r="D54">
-        <f>$F$31</f>
-        <v>4</v>
-      </c>
-      <c r="E54">
-        <v>0.35</v>
-      </c>
-      <c r="G54" t="str">
-        <f>'Inputs - Categorical'!C13</f>
-        <v>Bioenergy</v>
-      </c>
-      <c r="I54" t="str">
-        <f>'Inputs - Categorical'!$C$31</f>
-        <v>SPF</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" ht="16" customHeight="1">
+      <c r="D55">
+        <f>$F$27</f>
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="G55" t="str">
+        <f>'Inputs - Categorical'!C10</f>
+        <v>Sawnwood</v>
+      </c>
+      <c r="I55" t="str">
+        <f>'Inputs - Categorical'!$C$32</f>
+        <v>Hardwood</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" ht="16" customHeight="1">
       <c r="B56" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C56" t="str">
-        <f>$C$43</f>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D56">
         <f>$F$28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G56" t="str">
-        <f>'Inputs - Categorical'!C10</f>
-        <v>Sawnwood</v>
+        <f>'Inputs - Categorical'!C11</f>
+        <v>Panels</v>
       </c>
       <c r="I56" t="str">
         <f>'Inputs - Categorical'!$C$32</f>
         <v>Hardwood</v>
       </c>
     </row>
-    <row r="57" spans="2:10" ht="16" customHeight="1">
+    <row r="57" spans="2:9" ht="16" customHeight="1">
       <c r="B57" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C57" t="str">
-        <f t="shared" ref="C57:C59" si="3">$C$43</f>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D57">
         <f>$F$29</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="G57" t="str">
-        <f>'Inputs - Categorical'!C11</f>
-        <v>Panels</v>
+        <f>'Inputs - Categorical'!C12</f>
+        <v>Paper</v>
       </c>
       <c r="I57" t="str">
         <f>'Inputs - Categorical'!$C$32</f>
         <v>Hardwood</v>
       </c>
     </row>
-    <row r="58" spans="2:10" ht="16" customHeight="1">
+    <row r="58" spans="2:9" ht="16" customHeight="1">
       <c r="B58" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C58" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D58">
         <f>$F$30</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="G58" t="str">
-        <f>'Inputs - Categorical'!C12</f>
-        <v>Paper</v>
+        <f>'Inputs - Categorical'!C13</f>
+        <v>Bioenergy</v>
       </c>
       <c r="I58" t="str">
         <f>'Inputs - Categorical'!$C$32</f>
         <v>Hardwood</v>
       </c>
     </row>
-    <row r="59" spans="2:10" ht="16" customHeight="1">
-      <c r="B59" t="s">
-        <v>45</v>
-      </c>
-      <c r="C59" t="str">
-        <f t="shared" si="3"/>
+    <row r="60" spans="2:9" ht="16" customHeight="1">
+      <c r="B60" t="s">
+        <v>48</v>
+      </c>
+      <c r="C60" t="str">
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
-      <c r="D59">
-        <f>$F$31</f>
-        <v>4</v>
-      </c>
-      <c r="E59">
+      <c r="D60">
+        <f>$F$27</f>
+        <v>1</v>
+      </c>
+      <c r="E60">
         <v>0.35</v>
       </c>
-      <c r="G59" t="str">
-        <f>'Inputs - Categorical'!C13</f>
-        <v>Bioenergy</v>
-      </c>
-      <c r="I59" t="str">
-        <f>'Inputs - Categorical'!$C$32</f>
-        <v>Hardwood</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" ht="16" customHeight="1">
+      <c r="G60" t="str">
+        <f>'Inputs - Categorical'!C10</f>
+        <v>Sawnwood</v>
+      </c>
+      <c r="I60" t="str">
+        <f>'Inputs - Categorical'!$C$33</f>
+        <v>Hem-Fir</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" ht="16" customHeight="1">
       <c r="B61" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C61" t="str">
-        <f>$C$43</f>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D61">
         <f>$F$28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="G61" t="str">
-        <f>'Inputs - Categorical'!C10</f>
-        <v>Sawnwood</v>
+        <f>'Inputs - Categorical'!C11</f>
+        <v>Panels</v>
       </c>
       <c r="I61" t="str">
         <f>'Inputs - Categorical'!$C$33</f>
         <v>Hem-Fir</v>
       </c>
     </row>
-    <row r="62" spans="2:10" ht="16" customHeight="1">
+    <row r="62" spans="2:9" ht="16" customHeight="1">
       <c r="B62" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C62" t="str">
-        <f t="shared" ref="C62:C64" si="4">$C$43</f>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D62">
         <f>$F$29</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G62" t="str">
-        <f>'Inputs - Categorical'!C11</f>
-        <v>Panels</v>
+        <f>'Inputs - Categorical'!C12</f>
+        <v>Paper</v>
       </c>
       <c r="I62" t="str">
         <f>'Inputs - Categorical'!$C$33</f>
         <v>Hem-Fir</v>
       </c>
     </row>
-    <row r="63" spans="2:10" ht="16" customHeight="1">
+    <row r="63" spans="2:9" ht="16" customHeight="1">
       <c r="B63" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D63">
         <f>$F$30</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E63">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="G63" t="str">
-        <f>'Inputs - Categorical'!C12</f>
-        <v>Paper</v>
+        <f>'Inputs - Categorical'!C13</f>
+        <v>Bioenergy</v>
       </c>
       <c r="I63" t="str">
         <f>'Inputs - Categorical'!$C$33</f>
         <v>Hem-Fir</v>
       </c>
     </row>
-    <row r="64" spans="2:10" ht="16" customHeight="1">
-      <c r="B64" t="s">
-        <v>45</v>
-      </c>
-      <c r="C64" t="str">
-        <f t="shared" si="4"/>
+    <row r="65" spans="2:9" ht="16" customHeight="1">
+      <c r="B65" t="s">
+        <v>48</v>
+      </c>
+      <c r="C65" t="str">
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
-      <c r="D64">
-        <f>$F$31</f>
-        <v>4</v>
-      </c>
-      <c r="E64">
-        <v>0.4</v>
-      </c>
-      <c r="G64" t="str">
-        <f>'Inputs - Categorical'!C13</f>
-        <v>Bioenergy</v>
-      </c>
-      <c r="I64" t="str">
-        <f>'Inputs - Categorical'!$C$33</f>
-        <v>Hem-Fir</v>
+      <c r="D65">
+        <f>$F$27</f>
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>0.45</v>
+      </c>
+      <c r="G65" t="str">
+        <f>'Inputs - Categorical'!C10</f>
+        <v>Sawnwood</v>
+      </c>
+      <c r="I65" t="str">
+        <f>'Inputs - Categorical'!$C$34</f>
+        <v>DFL</v>
       </c>
     </row>
     <row r="66" spans="2:9" ht="16" customHeight="1">
       <c r="B66" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C66" t="str">
-        <f>$C$43</f>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D66">
         <f>$F$28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="G66" t="str">
-        <f>'Inputs - Categorical'!C10</f>
-        <v>Sawnwood</v>
+        <f>'Inputs - Categorical'!C11</f>
+        <v>Panels</v>
       </c>
       <c r="I66" t="str">
         <f>'Inputs - Categorical'!$C$34</f>
@@ -2438,22 +2154,22 @@
     </row>
     <row r="67" spans="2:9" ht="16" customHeight="1">
       <c r="B67" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C67" t="str">
-        <f t="shared" ref="C67:C69" si="5">$C$43</f>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D67">
         <f>$F$29</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67">
         <v>0.15</v>
       </c>
       <c r="G67" t="str">
-        <f>'Inputs - Categorical'!C11</f>
-        <v>Panels</v>
+        <f>'Inputs - Categorical'!C12</f>
+        <v>Paper</v>
       </c>
       <c r="I67" t="str">
         <f>'Inputs - Categorical'!$C$34</f>
@@ -2462,231 +2178,251 @@
     </row>
     <row r="68" spans="2:9" ht="16" customHeight="1">
       <c r="B68" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C68" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D68">
         <f>$F$30</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E68">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="G68" t="str">
-        <f>'Inputs - Categorical'!C12</f>
-        <v>Paper</v>
+        <f>'Inputs - Categorical'!C13</f>
+        <v>Bioenergy</v>
       </c>
       <c r="I68" t="str">
         <f>'Inputs - Categorical'!$C$34</f>
         <v>DFL</v>
       </c>
     </row>
-    <row r="69" spans="2:9" ht="16" customHeight="1">
-      <c r="B69" t="s">
-        <v>45</v>
-      </c>
-      <c r="C69" t="str">
-        <f t="shared" si="5"/>
+    <row r="70" spans="2:9" ht="16" customHeight="1">
+      <c r="B70" t="s">
+        <v>48</v>
+      </c>
+      <c r="C70" t="str">
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
-      <c r="D69">
-        <f>$F$31</f>
-        <v>4</v>
-      </c>
-      <c r="E69">
-        <v>0.25</v>
-      </c>
-      <c r="G69" t="str">
-        <f>'Inputs - Categorical'!C13</f>
-        <v>Bioenergy</v>
-      </c>
-      <c r="I69" t="str">
-        <f>'Inputs - Categorical'!$C$34</f>
-        <v>DFL</v>
+      <c r="D70">
+        <f>$F$27</f>
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="G70" t="str">
+        <f>'Inputs - Categorical'!$C$10</f>
+        <v>Sawnwood</v>
       </c>
     </row>
     <row r="71" spans="2:9" ht="16" customHeight="1">
       <c r="B71" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C71" t="str">
-        <f>$C$43</f>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D71">
         <f>$F$28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
       <c r="G71" t="str">
-        <f>'Inputs - Categorical'!C10</f>
-        <v>Sawnwood</v>
+        <f>'Inputs - Categorical'!$C$11</f>
+        <v>Panels</v>
       </c>
     </row>
     <row r="72" spans="2:9" ht="16" customHeight="1">
       <c r="B72" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C72" t="str">
-        <f t="shared" ref="C72:C74" si="6">$C$43</f>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D72">
         <f>$F$29</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="G72" t="str">
-        <f>'Inputs - Categorical'!C11</f>
-        <v>Panels</v>
+        <f>'Inputs - Categorical'!$C$12</f>
+        <v>Paper</v>
       </c>
     </row>
     <row r="73" spans="2:9" ht="16" customHeight="1">
       <c r="B73" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C73" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Commodity Demand, 1, CAT</v>
       </c>
       <c r="D73">
         <f>$F$30</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="str">
-        <f>'Inputs - Categorical'!C12</f>
-        <v>Paper</v>
-      </c>
-    </row>
-    <row r="74" spans="2:9" ht="16" customHeight="1">
-      <c r="B74" t="s">
-        <v>45</v>
-      </c>
-      <c r="C74" t="str">
-        <f t="shared" si="6"/>
-        <v>Commodity Demand, 1, CAT</v>
-      </c>
-      <c r="D74">
-        <f>$F$31</f>
-        <v>4</v>
-      </c>
-      <c r="E74">
+        <f>'Inputs - Categorical'!$C$13</f>
+        <v>Bioenergy</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" ht="16" customHeight="1">
+      <c r="B75" t="s">
+        <v>48</v>
+      </c>
+      <c r="C75" t="str">
+        <f t="shared" ref="C75:C83" si="8">$C$43</f>
+        <v>Commodity Demand, 2, CAT</v>
+      </c>
+      <c r="D75">
+        <f>$F$27</f>
         <v>1</v>
       </c>
-      <c r="G74" t="str">
-        <f>'Inputs - Categorical'!C13</f>
-        <v>Bioenergy</v>
+      <c r="F75">
+        <v>10</v>
+      </c>
+      <c r="G75" t="str">
+        <f>'Inputs - Categorical'!$C$10</f>
+        <v>Sawnwood</v>
       </c>
     </row>
     <row r="76" spans="2:9" ht="16" customHeight="1">
       <c r="B76" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C76" t="str">
-        <f>$C$44</f>
+        <f t="shared" si="8"/>
         <v>Commodity Demand, 2, CAT</v>
       </c>
       <c r="D76">
         <f>$F$28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="G76" t="str">
+        <f>'Inputs - Categorical'!$C$11</f>
+        <v>Panels</v>
       </c>
     </row>
     <row r="77" spans="2:9" ht="16" customHeight="1">
       <c r="B77" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C77" t="str">
-        <f t="shared" ref="C77:C79" si="7">$C$44</f>
+        <f t="shared" si="8"/>
         <v>Commodity Demand, 2, CAT</v>
       </c>
       <c r="D77">
         <f>$F$29</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="G77" t="str">
+        <f>'Inputs - Categorical'!$C$12</f>
+        <v>Paper</v>
       </c>
     </row>
     <row r="78" spans="2:9" ht="16" customHeight="1">
       <c r="B78" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C78" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Commodity Demand, 2, CAT</v>
       </c>
       <c r="D78">
         <f>$F$30</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F78">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="79" spans="2:9" ht="16" customHeight="1">
-      <c r="B79" t="s">
-        <v>45</v>
-      </c>
-      <c r="C79" t="str">
-        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G78" t="str">
+        <f>'Inputs - Categorical'!$C$13</f>
+        <v>Bioenergy</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" ht="16" customHeight="1">
+      <c r="B80" t="s">
+        <v>48</v>
+      </c>
+      <c r="C80" t="str">
+        <f t="shared" si="8"/>
         <v>Commodity Demand, 2, CAT</v>
       </c>
-      <c r="D79">
-        <f>$F$31</f>
-        <v>4</v>
-      </c>
-      <c r="F79">
+      <c r="D80">
+        <f>$F$27</f>
+        <v>1</v>
+      </c>
+      <c r="E80">
         <v>0</v>
+      </c>
+      <c r="G80" t="str">
+        <f>'Inputs - Categorical'!$C$10</f>
+        <v>Sawnwood</v>
       </c>
     </row>
     <row r="81" spans="2:8" ht="16" customHeight="1">
       <c r="B81" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C81" t="str">
-        <f>$C$44</f>
+        <f t="shared" si="8"/>
         <v>Commodity Demand, 2, CAT</v>
       </c>
       <c r="D81">
         <f>$F$28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81">
         <v>0</v>
       </c>
+      <c r="G81" t="str">
+        <f>'Inputs - Categorical'!$C$11</f>
+        <v>Panels</v>
+      </c>
     </row>
     <row r="82" spans="2:8" ht="16" customHeight="1">
       <c r="B82" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C82" t="str">
-        <f t="shared" ref="C82:C84" si="8">$C$44</f>
+        <f t="shared" si="8"/>
         <v>Commodity Demand, 2, CAT</v>
       </c>
       <c r="D82">
         <f>$F$29</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
+      <c r="G82" t="str">
+        <f>'Inputs - Categorical'!$C$12</f>
+        <v>Paper</v>
+      </c>
     </row>
     <row r="83" spans="2:8" ht="16" customHeight="1">
       <c r="B83" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C83" t="str">
         <f t="shared" si="8"/>
@@ -2694,42 +2430,58 @@
       </c>
       <c r="D83">
         <f>$F$30</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" ht="16" customHeight="1">
-      <c r="B84" t="s">
-        <v>45</v>
-      </c>
-      <c r="C84" t="str">
-        <f t="shared" si="8"/>
-        <v>Commodity Demand, 2, CAT</v>
-      </c>
-      <c r="D84">
-        <f>$F$31</f>
-        <v>4</v>
-      </c>
-      <c r="E84">
         <v>1</v>
+      </c>
+      <c r="G83" t="str">
+        <f>'Inputs - Categorical'!$C$13</f>
+        <v>Bioenergy</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" ht="16" customHeight="1">
+      <c r="B85" t="s">
+        <v>48</v>
+      </c>
+      <c r="C85" t="str">
+        <f t="shared" ref="C85:C108" si="9">$C$44</f>
+        <v>Commodity Demand, 3, CAT</v>
+      </c>
+      <c r="D85">
+        <f>$F$27</f>
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>0.5</v>
+      </c>
+      <c r="G85" t="str">
+        <f>'Inputs - Categorical'!$C$10</f>
+        <v>Sawnwood</v>
+      </c>
+      <c r="H85" t="str">
+        <f>'Inputs - Categorical'!$C$5</f>
+        <v>&gt; 8"</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="16" customHeight="1">
       <c r="B86" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C86" t="str">
-        <f>$C$45</f>
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D86">
         <f>$F$28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86">
-        <v>0.5</v>
+        <v>0.1</v>
+      </c>
+      <c r="G86" t="str">
+        <f>'Inputs - Categorical'!$C$11</f>
+        <v>Panels</v>
       </c>
       <c r="H86" t="str">
         <f>'Inputs - Categorical'!$C$5</f>
@@ -2738,18 +2490,22 @@
     </row>
     <row r="87" spans="2:8" ht="16" customHeight="1">
       <c r="B87" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C87" t="str">
-        <f t="shared" ref="C87:C89" si="9">$C$45</f>
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D87">
         <f>$F$29</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E87">
-        <v>0.1</v>
+        <v>0.3</v>
+      </c>
+      <c r="G87" t="str">
+        <f>'Inputs - Categorical'!$C$12</f>
+        <v>Paper</v>
       </c>
       <c r="H87" t="str">
         <f>'Inputs - Categorical'!$C$5</f>
@@ -2758,7 +2514,7 @@
     </row>
     <row r="88" spans="2:8" ht="16" customHeight="1">
       <c r="B88" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C88" t="str">
         <f t="shared" si="9"/>
@@ -2766,50 +2522,62 @@
       </c>
       <c r="D88">
         <f>$F$30</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E88">
-        <v>0.3</v>
+        <v>0.1</v>
+      </c>
+      <c r="G88" t="str">
+        <f>'Inputs - Categorical'!$C$13</f>
+        <v>Bioenergy</v>
       </c>
       <c r="H88" t="str">
         <f>'Inputs - Categorical'!$C$5</f>
         <v>&gt; 8"</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="16" customHeight="1">
-      <c r="B89" t="s">
-        <v>45</v>
-      </c>
-      <c r="C89" t="str">
+    <row r="90" spans="2:8" ht="16" customHeight="1">
+      <c r="B90" t="s">
+        <v>48</v>
+      </c>
+      <c r="C90" t="str">
         <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
-      <c r="D89">
-        <f>$F$31</f>
-        <v>4</v>
-      </c>
-      <c r="E89">
-        <v>0.1</v>
-      </c>
-      <c r="H89" t="str">
-        <f>'Inputs - Categorical'!$C$5</f>
-        <v>&gt; 8"</v>
+      <c r="D90">
+        <f>$F$27</f>
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>0.45</v>
+      </c>
+      <c r="G90" t="str">
+        <f>'Inputs - Categorical'!$C$10</f>
+        <v>Sawnwood</v>
+      </c>
+      <c r="H90" t="str">
+        <f>'Inputs - Categorical'!$C$6</f>
+        <v>6-8"</v>
       </c>
     </row>
     <row r="91" spans="2:8" ht="16" customHeight="1">
       <c r="B91" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C91" t="str">
-        <f>$C$45</f>
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D91">
         <f>$F$28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91">
-        <v>0.45</v>
+        <v>0.15</v>
+      </c>
+      <c r="G91" t="str">
+        <f>'Inputs - Categorical'!$C$11</f>
+        <v>Panels</v>
       </c>
       <c r="H91" t="str">
         <f>'Inputs - Categorical'!$C$6</f>
@@ -2818,18 +2586,22 @@
     </row>
     <row r="92" spans="2:8" ht="16" customHeight="1">
       <c r="B92" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C92" t="str">
-        <f t="shared" ref="C92:C94" si="10">$C$45</f>
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D92">
         <f>$F$29</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92">
-        <v>0.15</v>
+        <v>0.3</v>
+      </c>
+      <c r="G92" t="str">
+        <f>'Inputs - Categorical'!$C$12</f>
+        <v>Paper</v>
       </c>
       <c r="H92" t="str">
         <f>'Inputs - Categorical'!$C$6</f>
@@ -2838,58 +2610,70 @@
     </row>
     <row r="93" spans="2:8" ht="16" customHeight="1">
       <c r="B93" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C93" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D93">
         <f>$F$30</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E93">
-        <v>0.3</v>
+        <v>0.1</v>
+      </c>
+      <c r="G93" t="str">
+        <f>'Inputs - Categorical'!$C$13</f>
+        <v>Bioenergy</v>
       </c>
       <c r="H93" t="str">
         <f>'Inputs - Categorical'!$C$6</f>
         <v>6-8"</v>
       </c>
     </row>
-    <row r="94" spans="2:8" ht="16" customHeight="1">
-      <c r="B94" t="s">
-        <v>45</v>
-      </c>
-      <c r="C94" t="str">
-        <f t="shared" si="10"/>
+    <row r="95" spans="2:8" ht="16" customHeight="1">
+      <c r="B95" t="s">
+        <v>48</v>
+      </c>
+      <c r="C95" t="str">
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
-      <c r="D94">
-        <f>$F$31</f>
-        <v>4</v>
-      </c>
-      <c r="E94">
-        <v>0.1</v>
-      </c>
-      <c r="H94" t="str">
-        <f>'Inputs - Categorical'!$C$6</f>
-        <v>6-8"</v>
+      <c r="D95">
+        <f>$F$27</f>
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>0.3</v>
+      </c>
+      <c r="G95" t="str">
+        <f>'Inputs - Categorical'!$C$10</f>
+        <v>Sawnwood</v>
+      </c>
+      <c r="H95" t="str">
+        <f>'Inputs - Categorical'!$C$7</f>
+        <v>&lt; 6" clean</v>
       </c>
     </row>
     <row r="96" spans="2:8" ht="16" customHeight="1">
       <c r="B96" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C96" t="str">
-        <f>$C$45</f>
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D96">
         <f>$F$28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96">
-        <v>0.3</v>
+        <v>0.2</v>
+      </c>
+      <c r="G96" t="str">
+        <f>'Inputs - Categorical'!$C$11</f>
+        <v>Panels</v>
       </c>
       <c r="H96" t="str">
         <f>'Inputs - Categorical'!$C$7</f>
@@ -2898,18 +2682,22 @@
     </row>
     <row r="97" spans="2:8" ht="16" customHeight="1">
       <c r="B97" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C97" t="str">
-        <f t="shared" ref="C97:C99" si="11">$C$45</f>
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D97">
         <f>$F$29</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E97">
-        <v>0.2</v>
+        <v>0.4</v>
+      </c>
+      <c r="G97" t="str">
+        <f>'Inputs - Categorical'!$C$12</f>
+        <v>Paper</v>
       </c>
       <c r="H97" t="str">
         <f>'Inputs - Categorical'!$C$7</f>
@@ -2918,58 +2706,70 @@
     </row>
     <row r="98" spans="2:8" ht="16" customHeight="1">
       <c r="B98" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C98" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D98">
         <f>$F$30</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E98">
-        <v>0.4</v>
+        <v>0.1</v>
+      </c>
+      <c r="G98" t="str">
+        <f>'Inputs - Categorical'!$C$13</f>
+        <v>Bioenergy</v>
       </c>
       <c r="H98" t="str">
         <f>'Inputs - Categorical'!$C$7</f>
         <v>&lt; 6" clean</v>
       </c>
     </row>
-    <row r="99" spans="2:8" ht="16" customHeight="1">
-      <c r="B99" t="s">
-        <v>45</v>
-      </c>
-      <c r="C99" t="str">
-        <f t="shared" si="11"/>
+    <row r="100" spans="2:8" ht="16" customHeight="1">
+      <c r="B100" t="s">
+        <v>48</v>
+      </c>
+      <c r="C100" t="str">
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
-      <c r="D99">
-        <f>$F$31</f>
-        <v>4</v>
-      </c>
-      <c r="E99">
-        <v>0.1</v>
-      </c>
-      <c r="H99" t="str">
-        <f>'Inputs - Categorical'!$C$7</f>
-        <v>&lt; 6" clean</v>
+      <c r="D100">
+        <f>$F$27</f>
+        <v>1</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="G100" t="str">
+        <f>'Inputs - Categorical'!$C$10</f>
+        <v>Sawnwood</v>
+      </c>
+      <c r="H100" t="str">
+        <f>'Inputs - Categorical'!$C$8</f>
+        <v>&lt; 2" or contaminated</v>
       </c>
     </row>
     <row r="101" spans="2:8" ht="16" customHeight="1">
       <c r="B101" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C101" t="str">
-        <f>$C$45</f>
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D101">
         <f>$F$28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>0.1</v>
+      </c>
+      <c r="G101" t="str">
+        <f>'Inputs - Categorical'!$C$11</f>
+        <v>Panels</v>
       </c>
       <c r="H101" t="str">
         <f>'Inputs - Categorical'!$C$8</f>
@@ -2978,18 +2778,22 @@
     </row>
     <row r="102" spans="2:8" ht="16" customHeight="1">
       <c r="B102" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C102" t="str">
-        <f t="shared" ref="C102:C104" si="12">$C$45</f>
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D102">
         <f>$F$29</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E102">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="G102" t="str">
+        <f>'Inputs - Categorical'!$C$12</f>
+        <v>Paper</v>
       </c>
       <c r="H102" t="str">
         <f>'Inputs - Categorical'!$C$8</f>
@@ -2998,147 +2802,147 @@
     </row>
     <row r="103" spans="2:8" ht="16" customHeight="1">
       <c r="B103" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C103" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D103">
         <f>$F$30</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>0.9</v>
+      </c>
+      <c r="G103" t="str">
+        <f>'Inputs - Categorical'!$C$13</f>
+        <v>Bioenergy</v>
       </c>
       <c r="H103" t="str">
         <f>'Inputs - Categorical'!$C$8</f>
         <v>&lt; 2" or contaminated</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="16" customHeight="1">
-      <c r="B104" t="s">
-        <v>45</v>
-      </c>
-      <c r="C104" t="str">
-        <f t="shared" si="12"/>
+    <row r="105" spans="2:8" ht="16" customHeight="1">
+      <c r="B105" t="s">
+        <v>48</v>
+      </c>
+      <c r="C105" t="str">
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
-      <c r="D104">
-        <f>$F$31</f>
-        <v>4</v>
-      </c>
-      <c r="E104">
-        <v>0.9</v>
-      </c>
-      <c r="H104" t="str">
-        <f>'Inputs - Categorical'!$C$8</f>
-        <v>&lt; 2" or contaminated</v>
+      <c r="D105">
+        <f>$F$27</f>
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="G105" t="str">
+        <f>'Inputs - Categorical'!$C$10</f>
+        <v>Sawnwood</v>
       </c>
     </row>
     <row r="106" spans="2:8" ht="16" customHeight="1">
       <c r="B106" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C106" t="str">
-        <f>$C$45</f>
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D106">
         <f>$F$28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106">
         <v>0</v>
       </c>
+      <c r="G106" t="str">
+        <f>'Inputs - Categorical'!$C$11</f>
+        <v>Panels</v>
+      </c>
     </row>
     <row r="107" spans="2:8" ht="16" customHeight="1">
       <c r="B107" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C107" t="str">
-        <f t="shared" ref="C107:C109" si="13">$C$45</f>
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D107">
         <f>$F$29</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E107">
         <v>0</v>
       </c>
+      <c r="G107" t="str">
+        <f>'Inputs - Categorical'!$C$12</f>
+        <v>Paper</v>
+      </c>
     </row>
     <row r="108" spans="2:8" ht="16" customHeight="1">
       <c r="B108" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C108" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>Commodity Demand, 3, CAT</v>
       </c>
       <c r="D108">
         <f>$F$30</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" ht="16" customHeight="1">
-      <c r="B109" t="s">
-        <v>45</v>
-      </c>
-      <c r="C109" t="str">
-        <f t="shared" si="13"/>
-        <v>Commodity Demand, 3, CAT</v>
-      </c>
-      <c r="D109">
-        <f>$F$31</f>
-        <v>4</v>
-      </c>
-      <c r="E109">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="2:8" ht="16" customHeight="1">
-      <c r="B111" t="s">
-        <v>45</v>
-      </c>
-      <c r="C111" t="str">
-        <f>C47</f>
+      <c r="G108" t="str">
+        <f>'Inputs - Categorical'!$C$13</f>
+        <v>Bioenergy</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8" ht="16" customHeight="1">
+      <c r="B110" t="s">
+        <v>48</v>
+      </c>
+      <c r="C110" t="str">
+        <f>C46</f>
         <v>Combustion Parameters, CAT</v>
       </c>
-      <c r="D111">
+      <c r="D110">
         <v>1</v>
       </c>
-      <c r="E111">
+      <c r="E110">
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="2:5" ht="16" customHeight="1">
-      <c r="B113" t="s">
-        <v>45</v>
-      </c>
-      <c r="C113" t="str" cm="1">
-        <f t="array" ref="C113">C46</f>
+    <row r="112" spans="2:8" ht="16" customHeight="1">
+      <c r="B112" t="s">
+        <v>48</v>
+      </c>
+      <c r="C112" t="str" cm="1">
+        <f t="array" ref="C112">C45</f>
         <v>Landfill Parameters, CAT</v>
       </c>
-      <c r="D113">
+      <c r="D112">
         <v>1</v>
       </c>
-      <c r="E113">
+      <c r="E112">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22152807-D21A-1A49-9C05-E8FAC8B5CEA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:K15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
@@ -3152,41 +2956,41 @@
     <col min="11" max="11" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" s="3" customFormat="1">
+    <row r="1" spans="2:11" s="1" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>34</v>
+        <v>54</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="2:11">
       <c r="B2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C2" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -3205,7 +3009,7 @@
     </row>
     <row r="3" spans="2:11">
       <c r="B3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C3" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -3224,7 +3028,7 @@
     </row>
     <row r="4" spans="2:11">
       <c r="B4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C4" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -3243,7 +3047,7 @@
     </row>
     <row r="5" spans="2:11">
       <c r="B5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C5" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -3262,7 +3066,7 @@
     </row>
     <row r="6" spans="2:11">
       <c r="B6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C6" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -3281,7 +3085,7 @@
     </row>
     <row r="7" spans="2:11">
       <c r="B7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C7" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -3300,7 +3104,7 @@
     </row>
     <row r="8" spans="2:11">
       <c r="B8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C8" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -3319,7 +3123,7 @@
     </row>
     <row r="10" spans="2:11">
       <c r="B10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C10" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -3334,7 +3138,7 @@
     </row>
     <row r="12" spans="2:11">
       <c r="B12" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C12" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -3353,7 +3157,7 @@
     </row>
     <row r="13" spans="2:11">
       <c r="B13" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C13" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -3372,7 +3176,7 @@
     </row>
     <row r="14" spans="2:11">
       <c r="B14" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C14" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -3391,7 +3195,7 @@
     </row>
     <row r="15" spans="2:11">
       <c r="B15" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C15" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -3410,307 +3214,307 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{990EC481-AC22-9A46-B3DF-F781248D750D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:G49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" customWidth="1"/>
     <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" s="3" customFormat="1">
+    <row r="1" spans="2:5" s="1" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>57</v>
+      <c r="D1" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="B3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="B6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="B7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="B8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" s="3" customFormat="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" s="1" customFormat="1">
       <c r="B15" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" s="3" customFormat="1">
+      <c r="D15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" s="1" customFormat="1">
       <c r="B17" s="2" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" s="3" customFormat="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" s="1" customFormat="1">
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>34</v>
+      <c r="D19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="2:7">
       <c r="B21" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>121</v>
+        <v>78</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>122</v>
+        <v>78</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="2:7">
       <c r="B23" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>123</v>
+        <v>78</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="2:7">
       <c r="B24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>124</v>
+        <v>78</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="2:7">
       <c r="B25" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>125</v>
+        <v>78</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:7">
       <c r="B26" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>126</v>
+        <v>78</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="2:7">
       <c r="B27" t="s">
-        <v>109</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" s="3" customFormat="1">
+        <v>78</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" s="1" customFormat="1">
       <c r="B29" s="2" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>34</v>
+      <c r="D29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="2:7">
       <c r="B31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>116</v>
+        <v>87</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="2:7">
       <c r="B32" t="s">
-        <v>120</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>128</v>
+        <v>87</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>119</v>
+        <v>87</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" t="s">
-        <v>120</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" s="3" customFormat="1">
+        <v>87</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" s="1" customFormat="1">
       <c r="B36" s="2" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C38" t="str">
-        <f>$C$31</f>
+        <f t="shared" ref="C38:C40" si="0">$C$31</f>
         <v>SPF</v>
       </c>
       <c r="D38" t="str">
-        <f>C21</f>
+        <f t="shared" ref="D38:D40" si="1">C21</f>
         <v>Spruce</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C39" t="str">
-        <f t="shared" ref="C39:C40" si="0">$C$31</f>
+        <f t="shared" si="0"/>
         <v>SPF</v>
       </c>
       <c r="D39" t="str">
-        <f>C22</f>
+        <f t="shared" si="1"/>
         <v>Pine</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C40" t="str">
         <f t="shared" si="0"/>
         <v>SPF</v>
       </c>
       <c r="D40" t="str">
-        <f>C23</f>
+        <f t="shared" si="1"/>
         <v>Fir</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C42" t="str">
         <f>C32</f>
@@ -3723,7 +3527,7 @@
     </row>
     <row r="44" spans="2:4">
       <c r="B44" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C44" t="str">
         <f>C33</f>
@@ -3736,53 +3540,53 @@
     </row>
     <row r="46" spans="2:4">
       <c r="B46" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C46" t="str">
-        <f>$C$34</f>
+        <f t="shared" ref="C46:C47" si="2">$C$34</f>
         <v>DFL</v>
       </c>
       <c r="D46" t="str">
-        <f>C25</f>
+        <f t="shared" ref="D46:D47" si="3">C25</f>
         <v>Douglas-fir</v>
       </c>
     </row>
     <row r="47" spans="2:4">
       <c r="B47" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C47" t="str">
-        <f>$C$34</f>
+        <f t="shared" si="2"/>
         <v>DFL</v>
       </c>
       <c r="D47" t="str">
-        <f>C26</f>
+        <f t="shared" si="3"/>
         <v>Larch</v>
       </c>
     </row>
-    <row r="49" spans="2:5" s="3" customFormat="1">
+    <row r="49" spans="2:5" s="1" customFormat="1">
       <c r="B49" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C49" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>34</v>
+      <c r="D49" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FA93B2-6978-B84E-A9D8-E2FB98D2112C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
@@ -3796,46 +3600,46 @@
     <col min="8" max="8" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="3" customFormat="1">
+    <row r="1" spans="2:8" s="1" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D1" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>34</v>
+        <v>100</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="2:8">
       <c r="B2" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="C2">
         <v>1725</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E2">
         <v>998</v>
       </c>
     </row>
-    <row r="5" spans="2:8" s="3" customFormat="1">
+    <row r="5" spans="2:8" s="1" customFormat="1">
       <c r="B5" s="2" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>1</v>
@@ -3843,55 +3647,55 @@
     </row>
     <row r="6" spans="2:8">
       <c r="B6" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" s="3" customFormat="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" s="1" customFormat="1">
       <c r="B8" s="2" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>34</v>
+        <v>109</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D10" t="str">
         <f>C6</f>
         <v>Company</v>
       </c>
     </row>
-    <row r="13" spans="2:8" s="3" customFormat="1">
+    <row r="13" spans="2:8" s="1" customFormat="1">
       <c r="B13" s="2" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>86</v>
+        <v>112</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="C14" t="str">
         <f>C10</f>
@@ -3904,13 +3708,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B14A8909-7DF6-1B4A-B922-CF23C08FA7A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:F321"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
@@ -3921,79 +3725,79 @@
     <col min="6" max="6" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="3" customFormat="1">
+    <row r="1" spans="2:6" s="1" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>34</v>
+      <c r="D1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="2:6">
       <c r="B3" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" s="3" customFormat="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" s="1" customFormat="1">
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>34</v>
+      <c r="D7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="2:6">
       <c r="B9" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" s="3" customFormat="1">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" s="1" customFormat="1">
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="2:6">
       <c r="B14" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C14" t="str">
         <f>C9</f>
@@ -4004,32 +3808,32 @@
         <v>Gamma (2.07 80.2)</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:5" s="3" customFormat="1">
+    <row r="19" spans="2:5" s="1" customFormat="1">
       <c r="B19" s="2" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C21" t="str">
-        <f>$C$3</f>
+        <f t="shared" ref="C21:C84" si="0">$C$3</f>
         <v>Gamma (2.07 80.2)</v>
       </c>
       <c r="D21">
@@ -4041,10 +3845,10 @@
     </row>
     <row r="22" spans="2:5">
       <c r="B22" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C22" t="str">
-        <f t="shared" ref="C22:C85" si="0">$C$3</f>
+        <f t="shared" si="0"/>
         <v>Gamma (2.07 80.2)</v>
       </c>
       <c r="D22">
@@ -4056,7 +3860,7 @@
     </row>
     <row r="23" spans="2:5">
       <c r="B23" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -4071,7 +3875,7 @@
     </row>
     <row r="24" spans="2:5">
       <c r="B24" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -4086,7 +3890,7 @@
     </row>
     <row r="25" spans="2:5">
       <c r="B25" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -4101,7 +3905,7 @@
     </row>
     <row r="26" spans="2:5">
       <c r="B26" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -4116,7 +3920,7 @@
     </row>
     <row r="27" spans="2:5">
       <c r="B27" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -4131,7 +3935,7 @@
     </row>
     <row r="28" spans="2:5">
       <c r="B28" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -4146,7 +3950,7 @@
     </row>
     <row r="29" spans="2:5">
       <c r="B29" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -4161,7 +3965,7 @@
     </row>
     <row r="30" spans="2:5">
       <c r="B30" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -4176,7 +3980,7 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
@@ -4191,7 +3995,7 @@
     </row>
     <row r="32" spans="2:5">
       <c r="B32" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -4206,7 +4010,7 @@
     </row>
     <row r="33" spans="2:5">
       <c r="B33" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
@@ -4221,7 +4025,7 @@
     </row>
     <row r="34" spans="2:5">
       <c r="B34" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
@@ -4236,7 +4040,7 @@
     </row>
     <row r="35" spans="2:5">
       <c r="B35" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
@@ -4251,7 +4055,7 @@
     </row>
     <row r="36" spans="2:5">
       <c r="B36" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
@@ -4266,7 +4070,7 @@
     </row>
     <row r="37" spans="2:5">
       <c r="B37" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C37" t="str">
         <f t="shared" si="0"/>
@@ -4281,7 +4085,7 @@
     </row>
     <row r="38" spans="2:5">
       <c r="B38" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C38" t="str">
         <f t="shared" si="0"/>
@@ -4296,7 +4100,7 @@
     </row>
     <row r="39" spans="2:5">
       <c r="B39" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C39" t="str">
         <f t="shared" si="0"/>
@@ -4311,7 +4115,7 @@
     </row>
     <row r="40" spans="2:5">
       <c r="B40" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C40" t="str">
         <f t="shared" si="0"/>
@@ -4326,7 +4130,7 @@
     </row>
     <row r="41" spans="2:5">
       <c r="B41" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C41" t="str">
         <f t="shared" si="0"/>
@@ -4341,7 +4145,7 @@
     </row>
     <row r="42" spans="2:5">
       <c r="B42" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C42" t="str">
         <f t="shared" si="0"/>
@@ -4356,7 +4160,7 @@
     </row>
     <row r="43" spans="2:5">
       <c r="B43" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C43" t="str">
         <f t="shared" si="0"/>
@@ -4371,7 +4175,7 @@
     </row>
     <row r="44" spans="2:5">
       <c r="B44" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C44" t="str">
         <f t="shared" si="0"/>
@@ -4386,7 +4190,7 @@
     </row>
     <row r="45" spans="2:5">
       <c r="B45" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C45" t="str">
         <f t="shared" si="0"/>
@@ -4401,7 +4205,7 @@
     </row>
     <row r="46" spans="2:5">
       <c r="B46" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C46" t="str">
         <f t="shared" si="0"/>
@@ -4416,7 +4220,7 @@
     </row>
     <row r="47" spans="2:5">
       <c r="B47" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C47" t="str">
         <f t="shared" si="0"/>
@@ -4431,7 +4235,7 @@
     </row>
     <row r="48" spans="2:5">
       <c r="B48" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C48" t="str">
         <f t="shared" si="0"/>
@@ -4446,7 +4250,7 @@
     </row>
     <row r="49" spans="2:5">
       <c r="B49" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C49" t="str">
         <f t="shared" si="0"/>
@@ -4461,7 +4265,7 @@
     </row>
     <row r="50" spans="2:5">
       <c r="B50" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C50" t="str">
         <f t="shared" si="0"/>
@@ -4476,7 +4280,7 @@
     </row>
     <row r="51" spans="2:5">
       <c r="B51" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C51" t="str">
         <f t="shared" si="0"/>
@@ -4491,7 +4295,7 @@
     </row>
     <row r="52" spans="2:5">
       <c r="B52" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C52" t="str">
         <f t="shared" si="0"/>
@@ -4506,7 +4310,7 @@
     </row>
     <row r="53" spans="2:5">
       <c r="B53" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C53" t="str">
         <f t="shared" si="0"/>
@@ -4521,7 +4325,7 @@
     </row>
     <row r="54" spans="2:5">
       <c r="B54" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C54" t="str">
         <f t="shared" si="0"/>
@@ -4536,7 +4340,7 @@
     </row>
     <row r="55" spans="2:5">
       <c r="B55" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C55" t="str">
         <f t="shared" si="0"/>
@@ -4551,7 +4355,7 @@
     </row>
     <row r="56" spans="2:5">
       <c r="B56" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C56" t="str">
         <f t="shared" si="0"/>
@@ -4566,7 +4370,7 @@
     </row>
     <row r="57" spans="2:5">
       <c r="B57" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C57" t="str">
         <f t="shared" si="0"/>
@@ -4581,7 +4385,7 @@
     </row>
     <row r="58" spans="2:5">
       <c r="B58" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C58" t="str">
         <f t="shared" si="0"/>
@@ -4596,7 +4400,7 @@
     </row>
     <row r="59" spans="2:5">
       <c r="B59" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C59" t="str">
         <f t="shared" si="0"/>
@@ -4611,7 +4415,7 @@
     </row>
     <row r="60" spans="2:5">
       <c r="B60" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C60" t="str">
         <f t="shared" si="0"/>
@@ -4626,7 +4430,7 @@
     </row>
     <row r="61" spans="2:5">
       <c r="B61" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C61" t="str">
         <f t="shared" si="0"/>
@@ -4641,7 +4445,7 @@
     </row>
     <row r="62" spans="2:5">
       <c r="B62" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C62" t="str">
         <f t="shared" si="0"/>
@@ -4656,7 +4460,7 @@
     </row>
     <row r="63" spans="2:5">
       <c r="B63" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C63" t="str">
         <f t="shared" si="0"/>
@@ -4671,7 +4475,7 @@
     </row>
     <row r="64" spans="2:5">
       <c r="B64" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C64" t="str">
         <f t="shared" si="0"/>
@@ -4686,7 +4490,7 @@
     </row>
     <row r="65" spans="2:5">
       <c r="B65" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C65" t="str">
         <f t="shared" si="0"/>
@@ -4701,7 +4505,7 @@
     </row>
     <row r="66" spans="2:5">
       <c r="B66" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C66" t="str">
         <f t="shared" si="0"/>
@@ -4716,7 +4520,7 @@
     </row>
     <row r="67" spans="2:5">
       <c r="B67" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C67" t="str">
         <f t="shared" si="0"/>
@@ -4731,7 +4535,7 @@
     </row>
     <row r="68" spans="2:5">
       <c r="B68" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C68" t="str">
         <f t="shared" si="0"/>
@@ -4746,7 +4550,7 @@
     </row>
     <row r="69" spans="2:5">
       <c r="B69" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C69" t="str">
         <f t="shared" si="0"/>
@@ -4761,7 +4565,7 @@
     </row>
     <row r="70" spans="2:5">
       <c r="B70" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C70" t="str">
         <f t="shared" si="0"/>
@@ -4776,7 +4580,7 @@
     </row>
     <row r="71" spans="2:5">
       <c r="B71" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C71" t="str">
         <f t="shared" si="0"/>
@@ -4791,7 +4595,7 @@
     </row>
     <row r="72" spans="2:5">
       <c r="B72" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C72" t="str">
         <f t="shared" si="0"/>
@@ -4806,7 +4610,7 @@
     </row>
     <row r="73" spans="2:5">
       <c r="B73" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C73" t="str">
         <f t="shared" si="0"/>
@@ -4821,7 +4625,7 @@
     </row>
     <row r="74" spans="2:5">
       <c r="B74" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C74" t="str">
         <f t="shared" si="0"/>
@@ -4836,7 +4640,7 @@
     </row>
     <row r="75" spans="2:5">
       <c r="B75" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C75" t="str">
         <f t="shared" si="0"/>
@@ -4851,7 +4655,7 @@
     </row>
     <row r="76" spans="2:5">
       <c r="B76" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C76" t="str">
         <f t="shared" si="0"/>
@@ -4866,7 +4670,7 @@
     </row>
     <row r="77" spans="2:5">
       <c r="B77" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C77" t="str">
         <f t="shared" si="0"/>
@@ -4881,7 +4685,7 @@
     </row>
     <row r="78" spans="2:5">
       <c r="B78" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C78" t="str">
         <f t="shared" si="0"/>
@@ -4896,7 +4700,7 @@
     </row>
     <row r="79" spans="2:5">
       <c r="B79" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C79" t="str">
         <f t="shared" si="0"/>
@@ -4911,7 +4715,7 @@
     </row>
     <row r="80" spans="2:5">
       <c r="B80" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C80" t="str">
         <f t="shared" si="0"/>
@@ -4926,7 +4730,7 @@
     </row>
     <row r="81" spans="2:5">
       <c r="B81" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C81" t="str">
         <f t="shared" si="0"/>
@@ -4941,7 +4745,7 @@
     </row>
     <row r="82" spans="2:5">
       <c r="B82" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C82" t="str">
         <f t="shared" si="0"/>
@@ -4956,7 +4760,7 @@
     </row>
     <row r="83" spans="2:5">
       <c r="B83" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C83" t="str">
         <f t="shared" si="0"/>
@@ -4971,7 +4775,7 @@
     </row>
     <row r="84" spans="2:5">
       <c r="B84" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C84" t="str">
         <f t="shared" si="0"/>
@@ -4986,10 +4790,10 @@
     </row>
     <row r="85" spans="2:5">
       <c r="B85" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C85" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C85:C148" si="1">$C$3</f>
         <v>Gamma (2.07 80.2)</v>
       </c>
       <c r="D85">
@@ -5001,10 +4805,10 @@
     </row>
     <row r="86" spans="2:5">
       <c r="B86" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C86" t="str">
-        <f t="shared" ref="C86:C149" si="1">$C$3</f>
+        <f t="shared" si="1"/>
         <v>Gamma (2.07 80.2)</v>
       </c>
       <c r="D86">
@@ -5016,7 +4820,7 @@
     </row>
     <row r="87" spans="2:5">
       <c r="B87" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C87" t="str">
         <f t="shared" si="1"/>
@@ -5031,7 +4835,7 @@
     </row>
     <row r="88" spans="2:5">
       <c r="B88" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C88" t="str">
         <f t="shared" si="1"/>
@@ -5046,7 +4850,7 @@
     </row>
     <row r="89" spans="2:5">
       <c r="B89" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C89" t="str">
         <f t="shared" si="1"/>
@@ -5061,7 +4865,7 @@
     </row>
     <row r="90" spans="2:5">
       <c r="B90" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C90" t="str">
         <f t="shared" si="1"/>
@@ -5076,7 +4880,7 @@
     </row>
     <row r="91" spans="2:5">
       <c r="B91" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C91" t="str">
         <f t="shared" si="1"/>
@@ -5091,7 +4895,7 @@
     </row>
     <row r="92" spans="2:5">
       <c r="B92" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C92" t="str">
         <f t="shared" si="1"/>
@@ -5106,7 +4910,7 @@
     </row>
     <row r="93" spans="2:5">
       <c r="B93" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C93" t="str">
         <f t="shared" si="1"/>
@@ -5121,7 +4925,7 @@
     </row>
     <row r="94" spans="2:5">
       <c r="B94" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C94" t="str">
         <f t="shared" si="1"/>
@@ -5136,7 +4940,7 @@
     </row>
     <row r="95" spans="2:5">
       <c r="B95" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C95" t="str">
         <f t="shared" si="1"/>
@@ -5151,7 +4955,7 @@
     </row>
     <row r="96" spans="2:5">
       <c r="B96" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C96" t="str">
         <f t="shared" si="1"/>
@@ -5166,7 +4970,7 @@
     </row>
     <row r="97" spans="2:5">
       <c r="B97" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C97" t="str">
         <f t="shared" si="1"/>
@@ -5181,7 +4985,7 @@
     </row>
     <row r="98" spans="2:5">
       <c r="B98" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C98" t="str">
         <f t="shared" si="1"/>
@@ -5196,7 +5000,7 @@
     </row>
     <row r="99" spans="2:5">
       <c r="B99" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C99" t="str">
         <f t="shared" si="1"/>
@@ -5211,7 +5015,7 @@
     </row>
     <row r="100" spans="2:5">
       <c r="B100" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C100" t="str">
         <f t="shared" si="1"/>
@@ -5226,7 +5030,7 @@
     </row>
     <row r="101" spans="2:5">
       <c r="B101" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C101" t="str">
         <f t="shared" si="1"/>
@@ -5241,7 +5045,7 @@
     </row>
     <row r="102" spans="2:5">
       <c r="B102" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C102" t="str">
         <f t="shared" si="1"/>
@@ -5256,7 +5060,7 @@
     </row>
     <row r="103" spans="2:5">
       <c r="B103" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C103" t="str">
         <f t="shared" si="1"/>
@@ -5271,7 +5075,7 @@
     </row>
     <row r="104" spans="2:5">
       <c r="B104" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C104" t="str">
         <f t="shared" si="1"/>
@@ -5286,7 +5090,7 @@
     </row>
     <row r="105" spans="2:5">
       <c r="B105" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C105" t="str">
         <f t="shared" si="1"/>
@@ -5301,7 +5105,7 @@
     </row>
     <row r="106" spans="2:5">
       <c r="B106" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C106" t="str">
         <f t="shared" si="1"/>
@@ -5316,7 +5120,7 @@
     </row>
     <row r="107" spans="2:5">
       <c r="B107" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C107" t="str">
         <f t="shared" si="1"/>
@@ -5331,7 +5135,7 @@
     </row>
     <row r="108" spans="2:5">
       <c r="B108" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C108" t="str">
         <f t="shared" si="1"/>
@@ -5346,7 +5150,7 @@
     </row>
     <row r="109" spans="2:5">
       <c r="B109" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C109" t="str">
         <f t="shared" si="1"/>
@@ -5361,7 +5165,7 @@
     </row>
     <row r="110" spans="2:5">
       <c r="B110" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C110" t="str">
         <f t="shared" si="1"/>
@@ -5376,7 +5180,7 @@
     </row>
     <row r="111" spans="2:5">
       <c r="B111" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C111" t="str">
         <f t="shared" si="1"/>
@@ -5391,7 +5195,7 @@
     </row>
     <row r="112" spans="2:5">
       <c r="B112" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C112" t="str">
         <f t="shared" si="1"/>
@@ -5406,7 +5210,7 @@
     </row>
     <row r="113" spans="2:5">
       <c r="B113" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C113" t="str">
         <f t="shared" si="1"/>
@@ -5421,7 +5225,7 @@
     </row>
     <row r="114" spans="2:5">
       <c r="B114" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C114" t="str">
         <f t="shared" si="1"/>
@@ -5436,7 +5240,7 @@
     </row>
     <row r="115" spans="2:5">
       <c r="B115" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C115" t="str">
         <f t="shared" si="1"/>
@@ -5451,7 +5255,7 @@
     </row>
     <row r="116" spans="2:5">
       <c r="B116" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C116" t="str">
         <f t="shared" si="1"/>
@@ -5466,7 +5270,7 @@
     </row>
     <row r="117" spans="2:5">
       <c r="B117" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C117" t="str">
         <f t="shared" si="1"/>
@@ -5481,7 +5285,7 @@
     </row>
     <row r="118" spans="2:5">
       <c r="B118" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C118" t="str">
         <f t="shared" si="1"/>
@@ -5496,7 +5300,7 @@
     </row>
     <row r="119" spans="2:5">
       <c r="B119" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C119" t="str">
         <f t="shared" si="1"/>
@@ -5511,7 +5315,7 @@
     </row>
     <row r="120" spans="2:5">
       <c r="B120" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C120" t="str">
         <f t="shared" si="1"/>
@@ -5526,7 +5330,7 @@
     </row>
     <row r="121" spans="2:5">
       <c r="B121" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C121" t="str">
         <f t="shared" si="1"/>
@@ -5541,7 +5345,7 @@
     </row>
     <row r="122" spans="2:5">
       <c r="B122" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C122" t="str">
         <f t="shared" si="1"/>
@@ -5556,7 +5360,7 @@
     </row>
     <row r="123" spans="2:5">
       <c r="B123" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C123" t="str">
         <f t="shared" si="1"/>
@@ -5571,7 +5375,7 @@
     </row>
     <row r="124" spans="2:5">
       <c r="B124" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C124" t="str">
         <f t="shared" si="1"/>
@@ -5586,7 +5390,7 @@
     </row>
     <row r="125" spans="2:5">
       <c r="B125" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C125" t="str">
         <f t="shared" si="1"/>
@@ -5601,7 +5405,7 @@
     </row>
     <row r="126" spans="2:5">
       <c r="B126" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C126" t="str">
         <f t="shared" si="1"/>
@@ -5616,7 +5420,7 @@
     </row>
     <row r="127" spans="2:5">
       <c r="B127" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C127" t="str">
         <f t="shared" si="1"/>
@@ -5631,7 +5435,7 @@
     </row>
     <row r="128" spans="2:5">
       <c r="B128" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C128" t="str">
         <f t="shared" si="1"/>
@@ -5646,7 +5450,7 @@
     </row>
     <row r="129" spans="2:5">
       <c r="B129" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C129" t="str">
         <f t="shared" si="1"/>
@@ -5661,7 +5465,7 @@
     </row>
     <row r="130" spans="2:5">
       <c r="B130" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C130" t="str">
         <f t="shared" si="1"/>
@@ -5676,7 +5480,7 @@
     </row>
     <row r="131" spans="2:5">
       <c r="B131" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C131" t="str">
         <f t="shared" si="1"/>
@@ -5691,7 +5495,7 @@
     </row>
     <row r="132" spans="2:5">
       <c r="B132" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C132" t="str">
         <f t="shared" si="1"/>
@@ -5706,7 +5510,7 @@
     </row>
     <row r="133" spans="2:5">
       <c r="B133" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C133" t="str">
         <f t="shared" si="1"/>
@@ -5721,7 +5525,7 @@
     </row>
     <row r="134" spans="2:5">
       <c r="B134" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C134" t="str">
         <f t="shared" si="1"/>
@@ -5736,7 +5540,7 @@
     </row>
     <row r="135" spans="2:5">
       <c r="B135" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C135" t="str">
         <f t="shared" si="1"/>
@@ -5751,7 +5555,7 @@
     </row>
     <row r="136" spans="2:5">
       <c r="B136" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C136" t="str">
         <f t="shared" si="1"/>
@@ -5766,7 +5570,7 @@
     </row>
     <row r="137" spans="2:5">
       <c r="B137" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C137" t="str">
         <f t="shared" si="1"/>
@@ -5781,7 +5585,7 @@
     </row>
     <row r="138" spans="2:5">
       <c r="B138" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C138" t="str">
         <f t="shared" si="1"/>
@@ -5796,7 +5600,7 @@
     </row>
     <row r="139" spans="2:5">
       <c r="B139" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C139" t="str">
         <f t="shared" si="1"/>
@@ -5811,7 +5615,7 @@
     </row>
     <row r="140" spans="2:5">
       <c r="B140" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C140" t="str">
         <f t="shared" si="1"/>
@@ -5826,7 +5630,7 @@
     </row>
     <row r="141" spans="2:5">
       <c r="B141" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C141" t="str">
         <f t="shared" si="1"/>
@@ -5841,7 +5645,7 @@
     </row>
     <row r="142" spans="2:5">
       <c r="B142" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C142" t="str">
         <f t="shared" si="1"/>
@@ -5856,7 +5660,7 @@
     </row>
     <row r="143" spans="2:5">
       <c r="B143" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C143" t="str">
         <f t="shared" si="1"/>
@@ -5871,7 +5675,7 @@
     </row>
     <row r="144" spans="2:5">
       <c r="B144" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C144" t="str">
         <f t="shared" si="1"/>
@@ -5886,7 +5690,7 @@
     </row>
     <row r="145" spans="2:5">
       <c r="B145" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C145" t="str">
         <f t="shared" si="1"/>
@@ -5901,7 +5705,7 @@
     </row>
     <row r="146" spans="2:5">
       <c r="B146" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C146" t="str">
         <f t="shared" si="1"/>
@@ -5916,7 +5720,7 @@
     </row>
     <row r="147" spans="2:5">
       <c r="B147" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C147" t="str">
         <f t="shared" si="1"/>
@@ -5931,7 +5735,7 @@
     </row>
     <row r="148" spans="2:5">
       <c r="B148" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C148" t="str">
         <f t="shared" si="1"/>
@@ -5946,10 +5750,10 @@
     </row>
     <row r="149" spans="2:5">
       <c r="B149" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C149" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C149:C212" si="2">$C$3</f>
         <v>Gamma (2.07 80.2)</v>
       </c>
       <c r="D149">
@@ -5961,10 +5765,10 @@
     </row>
     <row r="150" spans="2:5">
       <c r="B150" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C150" t="str">
-        <f t="shared" ref="C150:C213" si="2">$C$3</f>
+        <f t="shared" si="2"/>
         <v>Gamma (2.07 80.2)</v>
       </c>
       <c r="D150">
@@ -5976,7 +5780,7 @@
     </row>
     <row r="151" spans="2:5">
       <c r="B151" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C151" t="str">
         <f t="shared" si="2"/>
@@ -5991,7 +5795,7 @@
     </row>
     <row r="152" spans="2:5">
       <c r="B152" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C152" t="str">
         <f t="shared" si="2"/>
@@ -6006,7 +5810,7 @@
     </row>
     <row r="153" spans="2:5">
       <c r="B153" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C153" t="str">
         <f t="shared" si="2"/>
@@ -6021,7 +5825,7 @@
     </row>
     <row r="154" spans="2:5">
       <c r="B154" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C154" t="str">
         <f t="shared" si="2"/>
@@ -6036,7 +5840,7 @@
     </row>
     <row r="155" spans="2:5">
       <c r="B155" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C155" t="str">
         <f t="shared" si="2"/>
@@ -6051,7 +5855,7 @@
     </row>
     <row r="156" spans="2:5">
       <c r="B156" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C156" t="str">
         <f t="shared" si="2"/>
@@ -6066,7 +5870,7 @@
     </row>
     <row r="157" spans="2:5">
       <c r="B157" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C157" t="str">
         <f t="shared" si="2"/>
@@ -6081,7 +5885,7 @@
     </row>
     <row r="158" spans="2:5">
       <c r="B158" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C158" t="str">
         <f t="shared" si="2"/>
@@ -6096,7 +5900,7 @@
     </row>
     <row r="159" spans="2:5">
       <c r="B159" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C159" t="str">
         <f t="shared" si="2"/>
@@ -6111,7 +5915,7 @@
     </row>
     <row r="160" spans="2:5">
       <c r="B160" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C160" t="str">
         <f t="shared" si="2"/>
@@ -6126,7 +5930,7 @@
     </row>
     <row r="161" spans="2:5">
       <c r="B161" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C161" t="str">
         <f t="shared" si="2"/>
@@ -6141,7 +5945,7 @@
     </row>
     <row r="162" spans="2:5">
       <c r="B162" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C162" t="str">
         <f t="shared" si="2"/>
@@ -6156,7 +5960,7 @@
     </row>
     <row r="163" spans="2:5">
       <c r="B163" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C163" t="str">
         <f t="shared" si="2"/>
@@ -6171,7 +5975,7 @@
     </row>
     <row r="164" spans="2:5">
       <c r="B164" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C164" t="str">
         <f t="shared" si="2"/>
@@ -6186,7 +5990,7 @@
     </row>
     <row r="165" spans="2:5">
       <c r="B165" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C165" t="str">
         <f t="shared" si="2"/>
@@ -6201,7 +6005,7 @@
     </row>
     <row r="166" spans="2:5">
       <c r="B166" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C166" t="str">
         <f t="shared" si="2"/>
@@ -6216,7 +6020,7 @@
     </row>
     <row r="167" spans="2:5">
       <c r="B167" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C167" t="str">
         <f t="shared" si="2"/>
@@ -6231,7 +6035,7 @@
     </row>
     <row r="168" spans="2:5">
       <c r="B168" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C168" t="str">
         <f t="shared" si="2"/>
@@ -6246,7 +6050,7 @@
     </row>
     <row r="169" spans="2:5">
       <c r="B169" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C169" t="str">
         <f t="shared" si="2"/>
@@ -6261,7 +6065,7 @@
     </row>
     <row r="170" spans="2:5">
       <c r="B170" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C170" t="str">
         <f t="shared" si="2"/>
@@ -6276,7 +6080,7 @@
     </row>
     <row r="171" spans="2:5">
       <c r="B171" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C171" t="str">
         <f t="shared" si="2"/>
@@ -6291,7 +6095,7 @@
     </row>
     <row r="172" spans="2:5">
       <c r="B172" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C172" t="str">
         <f t="shared" si="2"/>
@@ -6306,7 +6110,7 @@
     </row>
     <row r="173" spans="2:5">
       <c r="B173" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C173" t="str">
         <f t="shared" si="2"/>
@@ -6321,7 +6125,7 @@
     </row>
     <row r="174" spans="2:5">
       <c r="B174" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C174" t="str">
         <f t="shared" si="2"/>
@@ -6336,7 +6140,7 @@
     </row>
     <row r="175" spans="2:5">
       <c r="B175" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C175" t="str">
         <f t="shared" si="2"/>
@@ -6351,7 +6155,7 @@
     </row>
     <row r="176" spans="2:5">
       <c r="B176" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C176" t="str">
         <f t="shared" si="2"/>
@@ -6366,7 +6170,7 @@
     </row>
     <row r="177" spans="2:5">
       <c r="B177" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C177" t="str">
         <f t="shared" si="2"/>
@@ -6381,7 +6185,7 @@
     </row>
     <row r="178" spans="2:5">
       <c r="B178" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C178" t="str">
         <f t="shared" si="2"/>
@@ -6396,7 +6200,7 @@
     </row>
     <row r="179" spans="2:5">
       <c r="B179" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C179" t="str">
         <f t="shared" si="2"/>
@@ -6411,7 +6215,7 @@
     </row>
     <row r="180" spans="2:5">
       <c r="B180" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C180" t="str">
         <f t="shared" si="2"/>
@@ -6426,7 +6230,7 @@
     </row>
     <row r="181" spans="2:5">
       <c r="B181" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C181" t="str">
         <f t="shared" si="2"/>
@@ -6441,7 +6245,7 @@
     </row>
     <row r="182" spans="2:5">
       <c r="B182" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C182" t="str">
         <f t="shared" si="2"/>
@@ -6456,7 +6260,7 @@
     </row>
     <row r="183" spans="2:5">
       <c r="B183" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C183" t="str">
         <f t="shared" si="2"/>
@@ -6471,7 +6275,7 @@
     </row>
     <row r="184" spans="2:5">
       <c r="B184" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C184" t="str">
         <f t="shared" si="2"/>
@@ -6486,7 +6290,7 @@
     </row>
     <row r="185" spans="2:5">
       <c r="B185" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C185" t="str">
         <f t="shared" si="2"/>
@@ -6501,7 +6305,7 @@
     </row>
     <row r="186" spans="2:5">
       <c r="B186" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C186" t="str">
         <f t="shared" si="2"/>
@@ -6516,7 +6320,7 @@
     </row>
     <row r="187" spans="2:5">
       <c r="B187" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C187" t="str">
         <f t="shared" si="2"/>
@@ -6531,7 +6335,7 @@
     </row>
     <row r="188" spans="2:5">
       <c r="B188" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C188" t="str">
         <f t="shared" si="2"/>
@@ -6546,7 +6350,7 @@
     </row>
     <row r="189" spans="2:5">
       <c r="B189" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C189" t="str">
         <f t="shared" si="2"/>
@@ -6561,7 +6365,7 @@
     </row>
     <row r="190" spans="2:5">
       <c r="B190" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C190" t="str">
         <f t="shared" si="2"/>
@@ -6576,7 +6380,7 @@
     </row>
     <row r="191" spans="2:5">
       <c r="B191" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C191" t="str">
         <f t="shared" si="2"/>
@@ -6591,7 +6395,7 @@
     </row>
     <row r="192" spans="2:5">
       <c r="B192" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C192" t="str">
         <f t="shared" si="2"/>
@@ -6606,7 +6410,7 @@
     </row>
     <row r="193" spans="2:5">
       <c r="B193" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C193" t="str">
         <f t="shared" si="2"/>
@@ -6621,7 +6425,7 @@
     </row>
     <row r="194" spans="2:5">
       <c r="B194" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C194" t="str">
         <f t="shared" si="2"/>
@@ -6636,7 +6440,7 @@
     </row>
     <row r="195" spans="2:5">
       <c r="B195" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C195" t="str">
         <f t="shared" si="2"/>
@@ -6651,7 +6455,7 @@
     </row>
     <row r="196" spans="2:5">
       <c r="B196" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C196" t="str">
         <f t="shared" si="2"/>
@@ -6666,7 +6470,7 @@
     </row>
     <row r="197" spans="2:5">
       <c r="B197" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C197" t="str">
         <f t="shared" si="2"/>
@@ -6681,7 +6485,7 @@
     </row>
     <row r="198" spans="2:5">
       <c r="B198" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C198" t="str">
         <f t="shared" si="2"/>
@@ -6696,7 +6500,7 @@
     </row>
     <row r="199" spans="2:5">
       <c r="B199" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C199" t="str">
         <f t="shared" si="2"/>
@@ -6711,7 +6515,7 @@
     </row>
     <row r="200" spans="2:5">
       <c r="B200" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C200" t="str">
         <f t="shared" si="2"/>
@@ -6726,7 +6530,7 @@
     </row>
     <row r="201" spans="2:5">
       <c r="B201" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C201" t="str">
         <f t="shared" si="2"/>
@@ -6741,7 +6545,7 @@
     </row>
     <row r="202" spans="2:5">
       <c r="B202" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C202" t="str">
         <f t="shared" si="2"/>
@@ -6756,7 +6560,7 @@
     </row>
     <row r="203" spans="2:5">
       <c r="B203" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C203" t="str">
         <f t="shared" si="2"/>
@@ -6771,7 +6575,7 @@
     </row>
     <row r="204" spans="2:5">
       <c r="B204" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C204" t="str">
         <f t="shared" si="2"/>
@@ -6786,7 +6590,7 @@
     </row>
     <row r="205" spans="2:5">
       <c r="B205" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C205" t="str">
         <f t="shared" si="2"/>
@@ -6801,7 +6605,7 @@
     </row>
     <row r="206" spans="2:5">
       <c r="B206" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C206" t="str">
         <f t="shared" si="2"/>
@@ -6816,7 +6620,7 @@
     </row>
     <row r="207" spans="2:5">
       <c r="B207" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C207" t="str">
         <f t="shared" si="2"/>
@@ -6831,7 +6635,7 @@
     </row>
     <row r="208" spans="2:5">
       <c r="B208" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C208" t="str">
         <f t="shared" si="2"/>
@@ -6846,7 +6650,7 @@
     </row>
     <row r="209" spans="2:5">
       <c r="B209" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C209" t="str">
         <f t="shared" si="2"/>
@@ -6861,7 +6665,7 @@
     </row>
     <row r="210" spans="2:5">
       <c r="B210" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C210" t="str">
         <f t="shared" si="2"/>
@@ -6876,7 +6680,7 @@
     </row>
     <row r="211" spans="2:5">
       <c r="B211" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C211" t="str">
         <f t="shared" si="2"/>
@@ -6891,7 +6695,7 @@
     </row>
     <row r="212" spans="2:5">
       <c r="B212" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C212" t="str">
         <f t="shared" si="2"/>
@@ -6906,10 +6710,10 @@
     </row>
     <row r="213" spans="2:5">
       <c r="B213" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C213" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="C213:C276" si="3">$C$3</f>
         <v>Gamma (2.07 80.2)</v>
       </c>
       <c r="D213">
@@ -6921,10 +6725,10 @@
     </row>
     <row r="214" spans="2:5">
       <c r="B214" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C214" t="str">
-        <f t="shared" ref="C214:C277" si="3">$C$3</f>
+        <f t="shared" si="3"/>
         <v>Gamma (2.07 80.2)</v>
       </c>
       <c r="D214">
@@ -6936,7 +6740,7 @@
     </row>
     <row r="215" spans="2:5">
       <c r="B215" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C215" t="str">
         <f t="shared" si="3"/>
@@ -6951,7 +6755,7 @@
     </row>
     <row r="216" spans="2:5">
       <c r="B216" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C216" t="str">
         <f t="shared" si="3"/>
@@ -6966,7 +6770,7 @@
     </row>
     <row r="217" spans="2:5">
       <c r="B217" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C217" t="str">
         <f t="shared" si="3"/>
@@ -6981,7 +6785,7 @@
     </row>
     <row r="218" spans="2:5">
       <c r="B218" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C218" t="str">
         <f t="shared" si="3"/>
@@ -6996,7 +6800,7 @@
     </row>
     <row r="219" spans="2:5">
       <c r="B219" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C219" t="str">
         <f t="shared" si="3"/>
@@ -7011,7 +6815,7 @@
     </row>
     <row r="220" spans="2:5">
       <c r="B220" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C220" t="str">
         <f t="shared" si="3"/>
@@ -7026,7 +6830,7 @@
     </row>
     <row r="221" spans="2:5">
       <c r="B221" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C221" t="str">
         <f t="shared" si="3"/>
@@ -7041,7 +6845,7 @@
     </row>
     <row r="222" spans="2:5">
       <c r="B222" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C222" t="str">
         <f t="shared" si="3"/>
@@ -7056,7 +6860,7 @@
     </row>
     <row r="223" spans="2:5">
       <c r="B223" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C223" t="str">
         <f t="shared" si="3"/>
@@ -7071,7 +6875,7 @@
     </row>
     <row r="224" spans="2:5">
       <c r="B224" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C224" t="str">
         <f t="shared" si="3"/>
@@ -7086,7 +6890,7 @@
     </row>
     <row r="225" spans="2:5">
       <c r="B225" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C225" t="str">
         <f t="shared" si="3"/>
@@ -7101,7 +6905,7 @@
     </row>
     <row r="226" spans="2:5">
       <c r="B226" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C226" t="str">
         <f t="shared" si="3"/>
@@ -7116,7 +6920,7 @@
     </row>
     <row r="227" spans="2:5">
       <c r="B227" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C227" t="str">
         <f t="shared" si="3"/>
@@ -7131,7 +6935,7 @@
     </row>
     <row r="228" spans="2:5">
       <c r="B228" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C228" t="str">
         <f t="shared" si="3"/>
@@ -7146,7 +6950,7 @@
     </row>
     <row r="229" spans="2:5">
       <c r="B229" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C229" t="str">
         <f t="shared" si="3"/>
@@ -7161,7 +6965,7 @@
     </row>
     <row r="230" spans="2:5">
       <c r="B230" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C230" t="str">
         <f t="shared" si="3"/>
@@ -7176,7 +6980,7 @@
     </row>
     <row r="231" spans="2:5">
       <c r="B231" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C231" t="str">
         <f t="shared" si="3"/>
@@ -7191,7 +6995,7 @@
     </row>
     <row r="232" spans="2:5">
       <c r="B232" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C232" t="str">
         <f t="shared" si="3"/>
@@ -7206,7 +7010,7 @@
     </row>
     <row r="233" spans="2:5">
       <c r="B233" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C233" t="str">
         <f t="shared" si="3"/>
@@ -7221,7 +7025,7 @@
     </row>
     <row r="234" spans="2:5">
       <c r="B234" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C234" t="str">
         <f t="shared" si="3"/>
@@ -7236,7 +7040,7 @@
     </row>
     <row r="235" spans="2:5">
       <c r="B235" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C235" t="str">
         <f t="shared" si="3"/>
@@ -7251,7 +7055,7 @@
     </row>
     <row r="236" spans="2:5">
       <c r="B236" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C236" t="str">
         <f t="shared" si="3"/>
@@ -7266,7 +7070,7 @@
     </row>
     <row r="237" spans="2:5">
       <c r="B237" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C237" t="str">
         <f t="shared" si="3"/>
@@ -7281,7 +7085,7 @@
     </row>
     <row r="238" spans="2:5">
       <c r="B238" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C238" t="str">
         <f t="shared" si="3"/>
@@ -7296,7 +7100,7 @@
     </row>
     <row r="239" spans="2:5">
       <c r="B239" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C239" t="str">
         <f t="shared" si="3"/>
@@ -7311,7 +7115,7 @@
     </row>
     <row r="240" spans="2:5">
       <c r="B240" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C240" t="str">
         <f t="shared" si="3"/>
@@ -7326,7 +7130,7 @@
     </row>
     <row r="241" spans="2:5">
       <c r="B241" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C241" t="str">
         <f t="shared" si="3"/>
@@ -7341,7 +7145,7 @@
     </row>
     <row r="242" spans="2:5">
       <c r="B242" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C242" t="str">
         <f t="shared" si="3"/>
@@ -7356,7 +7160,7 @@
     </row>
     <row r="243" spans="2:5">
       <c r="B243" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C243" t="str">
         <f t="shared" si="3"/>
@@ -7371,7 +7175,7 @@
     </row>
     <row r="244" spans="2:5">
       <c r="B244" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C244" t="str">
         <f t="shared" si="3"/>
@@ -7386,7 +7190,7 @@
     </row>
     <row r="245" spans="2:5">
       <c r="B245" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C245" t="str">
         <f t="shared" si="3"/>
@@ -7401,7 +7205,7 @@
     </row>
     <row r="246" spans="2:5">
       <c r="B246" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C246" t="str">
         <f t="shared" si="3"/>
@@ -7416,7 +7220,7 @@
     </row>
     <row r="247" spans="2:5">
       <c r="B247" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C247" t="str">
         <f t="shared" si="3"/>
@@ -7431,7 +7235,7 @@
     </row>
     <row r="248" spans="2:5">
       <c r="B248" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C248" t="str">
         <f t="shared" si="3"/>
@@ -7446,7 +7250,7 @@
     </row>
     <row r="249" spans="2:5">
       <c r="B249" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C249" t="str">
         <f t="shared" si="3"/>
@@ -7461,7 +7265,7 @@
     </row>
     <row r="250" spans="2:5">
       <c r="B250" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C250" t="str">
         <f t="shared" si="3"/>
@@ -7476,7 +7280,7 @@
     </row>
     <row r="251" spans="2:5">
       <c r="B251" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C251" t="str">
         <f t="shared" si="3"/>
@@ -7491,7 +7295,7 @@
     </row>
     <row r="252" spans="2:5">
       <c r="B252" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C252" t="str">
         <f t="shared" si="3"/>
@@ -7506,7 +7310,7 @@
     </row>
     <row r="253" spans="2:5">
       <c r="B253" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C253" t="str">
         <f t="shared" si="3"/>
@@ -7521,7 +7325,7 @@
     </row>
     <row r="254" spans="2:5">
       <c r="B254" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C254" t="str">
         <f t="shared" si="3"/>
@@ -7536,7 +7340,7 @@
     </row>
     <row r="255" spans="2:5">
       <c r="B255" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C255" t="str">
         <f t="shared" si="3"/>
@@ -7551,7 +7355,7 @@
     </row>
     <row r="256" spans="2:5">
       <c r="B256" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C256" t="str">
         <f t="shared" si="3"/>
@@ -7566,7 +7370,7 @@
     </row>
     <row r="257" spans="2:5">
       <c r="B257" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C257" t="str">
         <f t="shared" si="3"/>
@@ -7581,7 +7385,7 @@
     </row>
     <row r="258" spans="2:5">
       <c r="B258" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C258" t="str">
         <f t="shared" si="3"/>
@@ -7596,7 +7400,7 @@
     </row>
     <row r="259" spans="2:5">
       <c r="B259" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C259" t="str">
         <f t="shared" si="3"/>
@@ -7611,7 +7415,7 @@
     </row>
     <row r="260" spans="2:5">
       <c r="B260" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C260" t="str">
         <f t="shared" si="3"/>
@@ -7626,7 +7430,7 @@
     </row>
     <row r="261" spans="2:5">
       <c r="B261" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C261" t="str">
         <f t="shared" si="3"/>
@@ -7641,7 +7445,7 @@
     </row>
     <row r="262" spans="2:5">
       <c r="B262" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C262" t="str">
         <f t="shared" si="3"/>
@@ -7656,7 +7460,7 @@
     </row>
     <row r="263" spans="2:5">
       <c r="B263" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C263" t="str">
         <f t="shared" si="3"/>
@@ -7671,7 +7475,7 @@
     </row>
     <row r="264" spans="2:5">
       <c r="B264" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C264" t="str">
         <f t="shared" si="3"/>
@@ -7686,7 +7490,7 @@
     </row>
     <row r="265" spans="2:5">
       <c r="B265" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C265" t="str">
         <f t="shared" si="3"/>
@@ -7701,7 +7505,7 @@
     </row>
     <row r="266" spans="2:5">
       <c r="B266" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C266" t="str">
         <f t="shared" si="3"/>
@@ -7716,7 +7520,7 @@
     </row>
     <row r="267" spans="2:5">
       <c r="B267" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C267" t="str">
         <f t="shared" si="3"/>
@@ -7731,7 +7535,7 @@
     </row>
     <row r="268" spans="2:5">
       <c r="B268" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C268" t="str">
         <f t="shared" si="3"/>
@@ -7746,7 +7550,7 @@
     </row>
     <row r="269" spans="2:5">
       <c r="B269" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C269" t="str">
         <f t="shared" si="3"/>
@@ -7761,7 +7565,7 @@
     </row>
     <row r="270" spans="2:5">
       <c r="B270" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C270" t="str">
         <f t="shared" si="3"/>
@@ -7776,7 +7580,7 @@
     </row>
     <row r="271" spans="2:5">
       <c r="B271" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C271" t="str">
         <f t="shared" si="3"/>
@@ -7791,7 +7595,7 @@
     </row>
     <row r="272" spans="2:5">
       <c r="B272" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C272" t="str">
         <f t="shared" si="3"/>
@@ -7806,7 +7610,7 @@
     </row>
     <row r="273" spans="2:5">
       <c r="B273" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C273" t="str">
         <f t="shared" si="3"/>
@@ -7821,7 +7625,7 @@
     </row>
     <row r="274" spans="2:5">
       <c r="B274" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C274" t="str">
         <f t="shared" si="3"/>
@@ -7836,7 +7640,7 @@
     </row>
     <row r="275" spans="2:5">
       <c r="B275" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C275" t="str">
         <f t="shared" si="3"/>
@@ -7851,7 +7655,7 @@
     </row>
     <row r="276" spans="2:5">
       <c r="B276" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C276" t="str">
         <f t="shared" si="3"/>
@@ -7866,10 +7670,10 @@
     </row>
     <row r="277" spans="2:5">
       <c r="B277" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C277" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="C277:C321" si="4">$C$3</f>
         <v>Gamma (2.07 80.2)</v>
       </c>
       <c r="D277">
@@ -7881,10 +7685,10 @@
     </row>
     <row r="278" spans="2:5">
       <c r="B278" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C278" t="str">
-        <f t="shared" ref="C278:C321" si="4">$C$3</f>
+        <f t="shared" si="4"/>
         <v>Gamma (2.07 80.2)</v>
       </c>
       <c r="D278">
@@ -7896,7 +7700,7 @@
     </row>
     <row r="279" spans="2:5">
       <c r="B279" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C279" t="str">
         <f t="shared" si="4"/>
@@ -7911,7 +7715,7 @@
     </row>
     <row r="280" spans="2:5">
       <c r="B280" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C280" t="str">
         <f t="shared" si="4"/>
@@ -7926,7 +7730,7 @@
     </row>
     <row r="281" spans="2:5">
       <c r="B281" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C281" t="str">
         <f t="shared" si="4"/>
@@ -7941,7 +7745,7 @@
     </row>
     <row r="282" spans="2:5">
       <c r="B282" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C282" t="str">
         <f t="shared" si="4"/>
@@ -7956,7 +7760,7 @@
     </row>
     <row r="283" spans="2:5">
       <c r="B283" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C283" t="str">
         <f t="shared" si="4"/>
@@ -7971,7 +7775,7 @@
     </row>
     <row r="284" spans="2:5">
       <c r="B284" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C284" t="str">
         <f t="shared" si="4"/>
@@ -7986,7 +7790,7 @@
     </row>
     <row r="285" spans="2:5">
       <c r="B285" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C285" t="str">
         <f t="shared" si="4"/>
@@ -8001,7 +7805,7 @@
     </row>
     <row r="286" spans="2:5">
       <c r="B286" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C286" t="str">
         <f t="shared" si="4"/>
@@ -8016,7 +7820,7 @@
     </row>
     <row r="287" spans="2:5">
       <c r="B287" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C287" t="str">
         <f t="shared" si="4"/>
@@ -8031,7 +7835,7 @@
     </row>
     <row r="288" spans="2:5">
       <c r="B288" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C288" t="str">
         <f t="shared" si="4"/>
@@ -8046,7 +7850,7 @@
     </row>
     <row r="289" spans="2:5">
       <c r="B289" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C289" t="str">
         <f t="shared" si="4"/>
@@ -8061,7 +7865,7 @@
     </row>
     <row r="290" spans="2:5">
       <c r="B290" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C290" t="str">
         <f t="shared" si="4"/>
@@ -8076,7 +7880,7 @@
     </row>
     <row r="291" spans="2:5">
       <c r="B291" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C291" t="str">
         <f t="shared" si="4"/>
@@ -8091,7 +7895,7 @@
     </row>
     <row r="292" spans="2:5">
       <c r="B292" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C292" t="str">
         <f t="shared" si="4"/>
@@ -8106,7 +7910,7 @@
     </row>
     <row r="293" spans="2:5">
       <c r="B293" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C293" t="str">
         <f t="shared" si="4"/>
@@ -8121,7 +7925,7 @@
     </row>
     <row r="294" spans="2:5">
       <c r="B294" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C294" t="str">
         <f t="shared" si="4"/>
@@ -8136,7 +7940,7 @@
     </row>
     <row r="295" spans="2:5">
       <c r="B295" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C295" t="str">
         <f t="shared" si="4"/>
@@ -8151,7 +7955,7 @@
     </row>
     <row r="296" spans="2:5">
       <c r="B296" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C296" t="str">
         <f t="shared" si="4"/>
@@ -8166,7 +7970,7 @@
     </row>
     <row r="297" spans="2:5">
       <c r="B297" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C297" t="str">
         <f t="shared" si="4"/>
@@ -8181,7 +7985,7 @@
     </row>
     <row r="298" spans="2:5">
       <c r="B298" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C298" t="str">
         <f t="shared" si="4"/>
@@ -8196,7 +8000,7 @@
     </row>
     <row r="299" spans="2:5">
       <c r="B299" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C299" t="str">
         <f t="shared" si="4"/>
@@ -8211,7 +8015,7 @@
     </row>
     <row r="300" spans="2:5">
       <c r="B300" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C300" t="str">
         <f t="shared" si="4"/>
@@ -8226,7 +8030,7 @@
     </row>
     <row r="301" spans="2:5">
       <c r="B301" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C301" t="str">
         <f t="shared" si="4"/>
@@ -8241,7 +8045,7 @@
     </row>
     <row r="302" spans="2:5">
       <c r="B302" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C302" t="str">
         <f t="shared" si="4"/>
@@ -8256,7 +8060,7 @@
     </row>
     <row r="303" spans="2:5">
       <c r="B303" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C303" t="str">
         <f t="shared" si="4"/>
@@ -8271,7 +8075,7 @@
     </row>
     <row r="304" spans="2:5">
       <c r="B304" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C304" t="str">
         <f t="shared" si="4"/>
@@ -8286,7 +8090,7 @@
     </row>
     <row r="305" spans="2:5">
       <c r="B305" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C305" t="str">
         <f t="shared" si="4"/>
@@ -8301,7 +8105,7 @@
     </row>
     <row r="306" spans="2:5">
       <c r="B306" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C306" t="str">
         <f t="shared" si="4"/>
@@ -8316,7 +8120,7 @@
     </row>
     <row r="307" spans="2:5">
       <c r="B307" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C307" t="str">
         <f t="shared" si="4"/>
@@ -8331,7 +8135,7 @@
     </row>
     <row r="308" spans="2:5">
       <c r="B308" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C308" t="str">
         <f t="shared" si="4"/>
@@ -8346,7 +8150,7 @@
     </row>
     <row r="309" spans="2:5">
       <c r="B309" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C309" t="str">
         <f t="shared" si="4"/>
@@ -8361,7 +8165,7 @@
     </row>
     <row r="310" spans="2:5">
       <c r="B310" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C310" t="str">
         <f t="shared" si="4"/>
@@ -8376,7 +8180,7 @@
     </row>
     <row r="311" spans="2:5">
       <c r="B311" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C311" t="str">
         <f t="shared" si="4"/>
@@ -8391,7 +8195,7 @@
     </row>
     <row r="312" spans="2:5">
       <c r="B312" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C312" t="str">
         <f t="shared" si="4"/>
@@ -8406,7 +8210,7 @@
     </row>
     <row r="313" spans="2:5">
       <c r="B313" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C313" t="str">
         <f t="shared" si="4"/>
@@ -8421,7 +8225,7 @@
     </row>
     <row r="314" spans="2:5">
       <c r="B314" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C314" t="str">
         <f t="shared" si="4"/>
@@ -8436,7 +8240,7 @@
     </row>
     <row r="315" spans="2:5">
       <c r="B315" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C315" t="str">
         <f t="shared" si="4"/>
@@ -8451,7 +8255,7 @@
     </row>
     <row r="316" spans="2:5">
       <c r="B316" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C316" t="str">
         <f t="shared" si="4"/>
@@ -8466,7 +8270,7 @@
     </row>
     <row r="317" spans="2:5">
       <c r="B317" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C317" t="str">
         <f t="shared" si="4"/>
@@ -8481,7 +8285,7 @@
     </row>
     <row r="318" spans="2:5">
       <c r="B318" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C318" t="str">
         <f t="shared" si="4"/>
@@ -8496,7 +8300,7 @@
     </row>
     <row r="319" spans="2:5">
       <c r="B319" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C319" t="str">
         <f t="shared" si="4"/>
@@ -8511,7 +8315,7 @@
     </row>
     <row r="320" spans="2:5">
       <c r="B320" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C320" t="str">
         <f t="shared" si="4"/>
@@ -8526,7 +8330,7 @@
     </row>
     <row r="321" spans="2:5">
       <c r="B321" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="C321" t="str">
         <f t="shared" si="4"/>
@@ -8551,6 +8355,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>